--- a/docs/data/jp/xlsx/2737.xlsx
+++ b/docs/data/jp/xlsx/2737.xlsx
@@ -1426,7 +1426,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -1696,7 +1696,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>부문 합계</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -7241,7 +7241,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Gain On Bad Debts Recovered EI</t>
+          <t>상각채권 추심이익</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
@@ -7379,7 +7379,7 @@
     <row r="105">
       <c r="A105" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Inventories EL</t>
+          <t>재고자산 평가손실</t>
         </is>
       </c>
       <c r="C105" s="20" t="n">
@@ -8559,7 +8559,7 @@
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>해외 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="E127" s="20" t="n">
@@ -8643,7 +8643,7 @@
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>해외 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="E130" s="20" t="n">
@@ -8727,7 +8727,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>해외 · 계</t>
         </is>
       </c>
       <c r="E133" s="20" t="n">
@@ -8811,7 +8811,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>해외 · 부문 이익</t>
         </is>
       </c>
       <c r="E136" s="20" t="n">

--- a/docs/data/jp/xlsx/2737.xlsx
+++ b/docs/data/jp/xlsx/2737.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,6 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -705,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC178"/>
+  <dimension ref="A1:AC197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4839,10 +4842,12 @@
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="n">
+        <v>32100</v>
+      </c>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="29" t="n"/>
       <c r="E53" s="29" t="n"/>
@@ -4877,7 +4882,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B54" s="27" t="n"/>
+      <c r="B54" s="27" t="n">
+        <v>6802000</v>
+      </c>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="29" t="n"/>
       <c r="E54" s="29" t="n"/>
@@ -6076,7 +6083,7 @@
     <row r="80">
       <c r="A80" s="41" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C80" s="39" t="n"/>
@@ -6328,1105 +6335,1229 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G85" s="15">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="15">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="15">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="15">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="15">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="15">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="15">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="15">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="15">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="15">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="15">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="15">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="15">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C85" s="20" t="n">
+      <c r="C86" s="20" t="n">
         <v>92245</v>
       </c>
-      <c r="D85" s="20" t="n">
+      <c r="D86" s="20" t="n">
         <v>81376</v>
       </c>
-      <c r="E85" s="20" t="n">
+      <c r="E86" s="20" t="n">
         <v>99309</v>
       </c>
-      <c r="F85" s="20" t="n">
+      <c r="F86" s="20" t="n">
         <v>98601</v>
       </c>
-      <c r="G85" s="20" t="n">
+      <c r="G86" s="20" t="n">
         <v>100702</v>
       </c>
-      <c r="H85" s="20" t="n">
+      <c r="H86" s="20" t="n">
         <v>96362</v>
       </c>
-      <c r="I85" s="20" t="n">
+      <c r="I86" s="20" t="n">
         <v>111309</v>
       </c>
-      <c r="J85" s="20" t="n">
+      <c r="J86" s="20" t="n">
         <v>99552</v>
       </c>
-      <c r="K85" s="20" t="n">
+      <c r="K86" s="20" t="n">
         <v>133296</v>
       </c>
-      <c r="L85" s="20" t="n">
+      <c r="L86" s="20" t="n">
         <v>144679</v>
       </c>
-      <c r="M85" s="20" t="n">
+      <c r="M86" s="20" t="n">
         <v>231939</v>
       </c>
-      <c r="N85" s="20" t="n">
+      <c r="N86" s="20" t="n">
         <v>371795</v>
       </c>
-      <c r="T85" s="20" t="n">
+      <c r="T86" s="20" t="n">
         <v>116166</v>
       </c>
-      <c r="U85" s="20" t="n">
+      <c r="U86" s="20" t="n">
         <v>82672</v>
       </c>
-      <c r="V85" s="20" t="n">
+      <c r="V86" s="20" t="n">
         <v>99309</v>
       </c>
-      <c r="W85" s="20" t="n">
+      <c r="W86" s="20" t="n">
         <v>111309</v>
       </c>
-      <c r="X85" s="20" t="n">
+      <c r="X86" s="20" t="n">
         <v>231939</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C86" s="12" t="n">
+      <c r="C87" s="12" t="n">
         <v>3568</v>
       </c>
-      <c r="D86" s="12" t="n">
+      <c r="D87" s="12" t="n">
         <v>2337</v>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="E87" s="12" t="n">
         <v>3872</v>
       </c>
-      <c r="F86" s="12" t="n">
+      <c r="F87" s="12" t="n">
         <v>4285</v>
       </c>
-      <c r="G86" s="12" t="n">
+      <c r="G87" s="12" t="n">
         <v>3716</v>
       </c>
-      <c r="H86" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>3846</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="I87" s="12" t="n">
         <v>2849</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="J87" s="12" t="n">
         <v>2833</v>
       </c>
-      <c r="K86" s="12" t="n">
+      <c r="K87" s="12" t="n">
         <v>7407</v>
       </c>
-      <c r="L86" s="12" t="n">
+      <c r="L87" s="12" t="n">
         <v>6579</v>
       </c>
-      <c r="M86" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>7383</v>
       </c>
-      <c r="N86" s="12" t="n">
+      <c r="N87" s="12" t="n">
         <v>23783</v>
       </c>
-      <c r="T86" s="12" t="n">
+      <c r="T87" s="12" t="n">
         <v>2966</v>
       </c>
-      <c r="U86" s="12" t="n">
+      <c r="U87" s="12" t="n">
         <v>2703</v>
       </c>
-      <c r="V86" s="12" t="n">
+      <c r="V87" s="12" t="n">
         <v>3872</v>
       </c>
-      <c r="W86" s="12" t="n">
+      <c r="W87" s="12" t="n">
         <v>2849</v>
       </c>
-      <c r="X86" s="12" t="n">
+      <c r="X87" s="12" t="n">
         <v>7383</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C87" s="20" t="n">
-        <v>992</v>
-      </c>
-      <c r="D87" s="20" t="n">
-        <v>922</v>
-      </c>
-      <c r="E87" s="20" t="n">
-        <v>1511</v>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>989</v>
-      </c>
-      <c r="G87" s="20" t="n">
-        <v>1023</v>
-      </c>
-      <c r="H87" s="20" t="n">
-        <v>1112</v>
-      </c>
-      <c r="I87" s="20" t="n">
-        <v>1403</v>
-      </c>
-      <c r="J87" s="20" t="n">
-        <v>986</v>
-      </c>
-      <c r="K87" s="20" t="n">
-        <v>1087</v>
-      </c>
-      <c r="L87" s="20" t="n">
-        <v>1346</v>
-      </c>
-      <c r="M87" s="20" t="n">
-        <v>1998</v>
-      </c>
-      <c r="N87" s="20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="T87" s="20" t="n">
-        <v>1277</v>
-      </c>
-      <c r="U87" s="20" t="n">
-        <v>1252</v>
-      </c>
-      <c r="V87" s="20" t="n">
-        <v>1511</v>
-      </c>
-      <c r="W87" s="20" t="n">
-        <v>1403</v>
-      </c>
-      <c r="X87" s="20" t="n">
-        <v>1998</v>
-      </c>
-    </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="n">
-        <v>2576</v>
-      </c>
-      <c r="D88" s="12" t="n">
-        <v>1416</v>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>2361</v>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>3295</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>2693</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>2735</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>1446</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>1846</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>6321</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>5233</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>5384</v>
-      </c>
-      <c r="N88" s="12" t="n">
-        <v>22282</v>
-      </c>
-      <c r="T88" s="12" t="n">
-        <v>1689</v>
-      </c>
-      <c r="U88" s="12" t="n">
-        <v>1451</v>
-      </c>
-      <c r="V88" s="12" t="n">
-        <v>2361</v>
-      </c>
-      <c r="W88" s="12" t="n">
-        <v>1446</v>
-      </c>
-      <c r="X88" s="12" t="n">
-        <v>5384</v>
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G88" s="15">
+        <f>IF(OR(G87="",C87=""),"",IF(C87&lt;=0,"",IFERROR(G87/C87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H88" s="15">
+        <f>IF(OR(H87="",D87=""),"",IF(D87&lt;=0,"",IFERROR(H87/D87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="15">
+        <f>IF(OR(I87="",E87=""),"",IF(E87&lt;=0,"",IFERROR(I87/E87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="15">
+        <f>IF(OR(J87="",F87=""),"",IF(F87&lt;=0,"",IFERROR(J87/F87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K88" s="15">
+        <f>IF(OR(K87="",G87=""),"",IF(G87&lt;=0,"",IFERROR(K87/G87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="15">
+        <f>IF(OR(L87="",H87=""),"",IF(H87&lt;=0,"",IFERROR(L87/H87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M88" s="15">
+        <f>IF(OR(M87="",I87=""),"",IF(I87&lt;=0,"",IFERROR(M87/I87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="15">
+        <f>IF(OR(N87="",J87=""),"",IF(J87&lt;=0,"",IFERROR(N87/J87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T88" s="15">
+        <f>IF(OR(T87="",S87=""),"",IF(S87&lt;=0,"",IFERROR(T87/S87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U88" s="15">
+        <f>IF(OR(U87="",T87=""),"",IF(T87&lt;=0,"",IFERROR(U87/T87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V88" s="15">
+        <f>IF(OR(V87="",U87=""),"",IF(U87&lt;=0,"",IFERROR(V87/U87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W88" s="15">
+        <f>IF(OR(W87="",V87=""),"",IF(V87&lt;=0,"",IFERROR(W87/V87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X88" s="15">
+        <f>IF(OR(X87="",W87=""),"",IF(W87&lt;=0,"",IFERROR(X87/W87-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C89" s="20" t="n">
-        <v>1</v>
+        <v>992</v>
       </c>
       <c r="D89" s="20" t="n">
-        <v>3</v>
+        <v>922</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>2</v>
+        <v>1511</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>8</v>
+        <v>989</v>
       </c>
       <c r="G89" s="20" t="n">
-        <v>6</v>
+        <v>1023</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>12</v>
+        <v>1112</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>9</v>
+        <v>1403</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>13</v>
+        <v>986</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>9</v>
+        <v>1087</v>
       </c>
       <c r="L89" s="20" t="n">
-        <v>11</v>
+        <v>1346</v>
       </c>
       <c r="M89" s="20" t="n">
-        <v>4</v>
+        <v>1998</v>
       </c>
       <c r="N89" s="20" t="n">
-        <v>5</v>
+        <v>1500</v>
       </c>
       <c r="T89" s="20" t="n">
-        <v>1</v>
+        <v>1277</v>
       </c>
       <c r="U89" s="20" t="n">
-        <v>0</v>
+        <v>1252</v>
       </c>
       <c r="V89" s="20" t="n">
-        <v>2</v>
+        <v>1511</v>
       </c>
       <c r="W89" s="20" t="n">
-        <v>9</v>
+        <v>1403</v>
       </c>
       <c r="X89" s="20" t="n">
-        <v>4</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="20" t="n">
-        <v>0</v>
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>2576</v>
+      </c>
+      <c r="D90" s="12" t="n">
+        <v>1416</v>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>2361</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>3295</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>2693</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>2735</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>1446</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>1846</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>6321</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>5233</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>5384</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>22282</v>
+      </c>
+      <c r="T90" s="12" t="n">
+        <v>1689</v>
+      </c>
+      <c r="U90" s="12" t="n">
+        <v>1451</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>2361</v>
+      </c>
+      <c r="W90" s="12" t="n">
+        <v>1446</v>
+      </c>
+      <c r="X90" s="12" t="n">
+        <v>5384</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="20" t="n">
-        <v>651</v>
-      </c>
-      <c r="J91" s="20" t="n">
-        <v>349</v>
-      </c>
-      <c r="K91" s="20" t="n">
-        <v>-349</v>
-      </c>
-      <c r="N91" s="20" t="n">
-        <v>0</v>
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C91" s="15">
+        <f>IF(OR(C90="",C84=""),"",IF(C84&lt;=0,"",IFERROR(C90/C84,"")))</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>IF(OR(D90="",D84=""),"",IF(D84&lt;=0,"",IFERROR(D90/D84,"")))</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>IF(OR(E90="",E84=""),"",IF(E84&lt;=0,"",IFERROR(E90/E84,"")))</f>
+        <v/>
+      </c>
+      <c r="F91" s="15">
+        <f>IF(OR(F90="",F84=""),"",IF(F84&lt;=0,"",IFERROR(F90/F84,"")))</f>
+        <v/>
+      </c>
+      <c r="G91" s="15">
+        <f>IF(OR(G90="",G84=""),"",IF(G84&lt;=0,"",IFERROR(G90/G84,"")))</f>
+        <v/>
+      </c>
+      <c r="H91" s="15">
+        <f>IF(OR(H90="",H84=""),"",IF(H84&lt;=0,"",IFERROR(H90/H84,"")))</f>
+        <v/>
+      </c>
+      <c r="I91" s="15">
+        <f>IF(OR(I90="",I84=""),"",IF(I84&lt;=0,"",IFERROR(I90/I84,"")))</f>
+        <v/>
+      </c>
+      <c r="J91" s="15">
+        <f>IF(OR(J90="",J84=""),"",IF(J84&lt;=0,"",IFERROR(J90/J84,"")))</f>
+        <v/>
+      </c>
+      <c r="K91" s="15">
+        <f>IF(OR(K90="",K84=""),"",IF(K84&lt;=0,"",IFERROR(K90/K84,"")))</f>
+        <v/>
+      </c>
+      <c r="L91" s="15">
+        <f>IF(OR(L90="",L84=""),"",IF(L84&lt;=0,"",IFERROR(L90/L84,"")))</f>
+        <v/>
+      </c>
+      <c r="M91" s="15">
+        <f>IF(OR(M90="",M84=""),"",IF(M84&lt;=0,"",IFERROR(M90/M84,"")))</f>
+        <v/>
+      </c>
+      <c r="N91" s="15">
+        <f>IF(OR(N90="",N84=""),"",IF(N84&lt;=0,"",IFERROR(N90/N84,"")))</f>
+        <v/>
+      </c>
+      <c r="T91" s="15">
+        <f>IF(OR(T90="",T84=""),"",IF(T84&lt;=0,"",IFERROR(T90/T84,"")))</f>
+        <v/>
+      </c>
+      <c r="U91" s="15">
+        <f>IF(OR(U90="",U84=""),"",IF(U84&lt;=0,"",IFERROR(U90/U84,"")))</f>
+        <v/>
+      </c>
+      <c r="V91" s="15">
+        <f>IF(OR(V90="",V84=""),"",IF(V84&lt;=0,"",IFERROR(V90/V84,"")))</f>
+        <v/>
+      </c>
+      <c r="W91" s="15">
+        <f>IF(OR(W90="",W84=""),"",IF(W84&lt;=0,"",IFERROR(W90/W84,"")))</f>
+        <v/>
+      </c>
+      <c r="X91" s="15">
+        <f>IF(OR(X90="",X84=""),"",IF(X84&lt;=0,"",IFERROR(X90/X84,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>지분법이익</t>
-        </is>
-      </c>
-      <c r="C92" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="20" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E92" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="F92" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G92" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H92" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I92" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J92" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K92" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L92" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="M92" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N92" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="T92" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="U92" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V92" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="W92" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X92" s="20" t="n">
-        <v>8</v>
+      <c r="A92" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G92" s="15">
+        <f>IF(OR(G90="",C90=""),"",IF(C90&lt;=0,"",IFERROR(G90/C90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H92" s="15">
+        <f>IF(OR(H90="",D90=""),"",IF(D90&lt;=0,"",IFERROR(H90/D90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I92" s="15">
+        <f>IF(OR(I90="",E90=""),"",IF(E90&lt;=0,"",IFERROR(I90/E90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J92" s="15">
+        <f>IF(OR(J90="",F90=""),"",IF(F90&lt;=0,"",IFERROR(J90/F90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K92" s="15">
+        <f>IF(OR(K90="",G90=""),"",IF(G90&lt;=0,"",IFERROR(K90/G90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L92" s="15">
+        <f>IF(OR(L90="",H90=""),"",IF(H90&lt;=0,"",IFERROR(L90/H90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M92" s="15">
+        <f>IF(OR(M90="",I90=""),"",IF(I90&lt;=0,"",IFERROR(M90/I90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N92" s="15">
+        <f>IF(OR(N90="",J90=""),"",IF(J90&lt;=0,"",IFERROR(N90/J90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T92" s="15">
+        <f>IF(OR(T90="",S90=""),"",IF(S90&lt;=0,"",IFERROR(T90/S90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U92" s="15">
+        <f>IF(OR(U90="",T90=""),"",IF(T90&lt;=0,"",IFERROR(U90/T90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V92" s="15">
+        <f>IF(OR(V90="",U90=""),"",IF(U90&lt;=0,"",IFERROR(V90/U90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W92" s="15">
+        <f>IF(OR(W90="",V90=""),"",IF(V90&lt;=0,"",IFERROR(W90/V90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X92" s="15">
+        <f>IF(OR(X90="",W90=""),"",IF(W90&lt;=0,"",IFERROR(X90/W90-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C93" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93" s="20" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="E93" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F93" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G93" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I93" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J93" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="K93" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="L93" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M93" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N93" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" s="20" t="n">
         <v>0</v>
-      </c>
-      <c r="G93" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="H93" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I93" s="20" t="n">
-        <v>-19</v>
-      </c>
-      <c r="J93" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K93" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="M93" s="20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="N93" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="T93" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="U93" s="20" t="n">
-        <v>14</v>
       </c>
       <c r="V93" s="20" t="n">
         <v>2</v>
       </c>
       <c r="W93" s="20" t="n">
-        <v>-19</v>
+        <v>9</v>
       </c>
       <c r="X93" s="20" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D94" s="20" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E94" s="20" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="F94" s="20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G94" s="20" t="n">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>-617</v>
+        <v>0</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J94" s="20" t="n">
-        <v>373</v>
-      </c>
-      <c r="K94" s="20" t="n">
-        <v>-333</v>
-      </c>
-      <c r="L94" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="M94" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="N94" s="20" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="T94" s="20" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="U94" s="20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V94" s="20" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="W94" s="20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="X94" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C95" s="20" t="n">
-        <v>458</v>
-      </c>
-      <c r="D95" s="20" t="n">
-        <v>222</v>
-      </c>
-      <c r="E95" s="20" t="n">
-        <v>408</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F95" s="20" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="G95" s="20" t="n">
-        <v>569</v>
-      </c>
-      <c r="H95" s="20" t="n">
-        <v>406</v>
-      </c>
-      <c r="I95" s="20" t="n">
-        <v>453</v>
+        <v>651</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>509</v>
-      </c>
-      <c r="L95" s="20" t="n">
-        <v>552</v>
-      </c>
-      <c r="M95" s="20" t="n">
-        <v>662</v>
+        <v>-349</v>
       </c>
       <c r="N95" s="20" t="n">
-        <v>1216</v>
-      </c>
-      <c r="T95" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="U95" s="20" t="n">
-        <v>356</v>
-      </c>
-      <c r="V95" s="20" t="n">
-        <v>408</v>
-      </c>
-      <c r="W95" s="20" t="n">
-        <v>453</v>
-      </c>
-      <c r="X95" s="20" t="n">
-        <v>662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>채권매각손실</t>
+          <t>지분법이익</t>
         </is>
       </c>
       <c r="C96" s="20" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D96" s="20" t="n">
-        <v>128</v>
+        <v>-6</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>136</v>
+        <v>-2</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="T96" s="20" t="n">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="U96" s="20" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="V96" s="20" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="W96" s="20" t="n">
-        <v>136</v>
+        <v>-2</v>
       </c>
       <c r="X96" s="20" t="n">
-        <v>109</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
-        <v>734</v>
+        <v>5</v>
       </c>
       <c r="D97" s="20" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>483</v>
+        <v>2</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="G97" s="20" t="n">
-        <v>-815</v>
+        <v>7</v>
       </c>
       <c r="H97" s="20" t="n">
-        <v>712</v>
+        <v>17</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>-165</v>
+        <v>-19</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="L97" s="20" t="n">
-        <v>1161</v>
+        <v>14</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>1667</v>
+        <v>-10</v>
       </c>
       <c r="N97" s="20" t="n">
-        <v>1088</v>
+        <v>11</v>
       </c>
       <c r="T97" s="20" t="n">
-        <v>923</v>
+        <v>8</v>
       </c>
       <c r="U97" s="20" t="n">
-        <v>353</v>
+        <v>14</v>
       </c>
       <c r="V97" s="20" t="n">
-        <v>483</v>
+        <v>2</v>
       </c>
       <c r="W97" s="20" t="n">
-        <v>-165</v>
+        <v>-19</v>
       </c>
       <c r="X97" s="20" t="n">
-        <v>1667</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D98" s="20" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="E98" s="20" t="n">
-        <v>4</v>
+        <v>369</v>
       </c>
       <c r="F98" s="20" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G98" s="20" t="n">
-        <v>8</v>
+        <v>669</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>10</v>
+        <v>-617</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>9</v>
+        <v>373</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>10</v>
+        <v>-333</v>
       </c>
       <c r="L98" s="20" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="M98" s="20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="N98" s="20" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="T98" s="20" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="U98" s="20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="V98" s="20" t="n">
-        <v>4</v>
+        <v>369</v>
       </c>
       <c r="W98" s="20" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="X98" s="20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C99" s="20" t="n">
-        <v>1270</v>
+        <v>458</v>
       </c>
       <c r="D99" s="20" t="n">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>1012</v>
+        <v>408</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>1250</v>
+        <v>370</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>-117</v>
+        <v>569</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>1300</v>
+        <v>406</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>511</v>
+        <v>343</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>699</v>
+        <v>509</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>1861</v>
+        <v>552</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>2469</v>
+        <v>662</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>2622</v>
+        <v>1216</v>
       </c>
       <c r="T99" s="20" t="n">
-        <v>1070</v>
+        <v>31</v>
       </c>
       <c r="U99" s="20" t="n">
-        <v>734</v>
+        <v>356</v>
       </c>
       <c r="V99" s="20" t="n">
-        <v>1012</v>
+        <v>408</v>
       </c>
       <c r="W99" s="20" t="n">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="X99" s="20" t="n">
-        <v>2469</v>
+        <v>662</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>1315</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>1073</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>1717</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>2072</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>3480</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>816</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>1009</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>1709</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>5288</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>3408</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>2917</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>19741</v>
-      </c>
-      <c r="T100" s="12" t="n">
-        <v>656</v>
-      </c>
-      <c r="U100" s="12" t="n">
-        <v>728</v>
-      </c>
-      <c r="V100" s="12" t="n">
-        <v>1717</v>
-      </c>
-      <c r="W100" s="12" t="n">
-        <v>1009</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>2917</v>
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>채권매각손실</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="D100" s="20" t="n">
+        <v>128</v>
+      </c>
+      <c r="E100" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="F100" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="G100" s="20" t="n">
+        <v>122</v>
+      </c>
+      <c r="H100" s="20" t="n">
+        <v>172</v>
+      </c>
+      <c r="I100" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="J100" s="20" t="n">
+        <v>159</v>
+      </c>
+      <c r="K100" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="L100" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="M100" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="N100" s="20" t="n">
+        <v>289</v>
+      </c>
+      <c r="T100" s="20" t="n">
+        <v>113</v>
+      </c>
+      <c r="U100" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="V100" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="W100" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="X100" s="20" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="C101" s="20" t="n">
-        <v>54</v>
+        <v>734</v>
       </c>
       <c r="D101" s="20" t="n">
+        <v>-22</v>
+      </c>
+      <c r="E101" s="20" t="n">
+        <v>483</v>
+      </c>
+      <c r="F101" s="20" t="n">
+        <v>815</v>
+      </c>
+      <c r="G101" s="20" t="n">
+        <v>-815</v>
+      </c>
+      <c r="H101" s="20" t="n">
+        <v>712</v>
+      </c>
+      <c r="I101" s="20" t="n">
+        <v>-165</v>
+      </c>
+      <c r="J101" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="20" t="n">
-        <v>0</v>
+      <c r="K101" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="L101" s="20" t="n">
+        <v>1161</v>
+      </c>
+      <c r="M101" s="20" t="n">
+        <v>1667</v>
+      </c>
+      <c r="N101" s="20" t="n">
+        <v>1088</v>
+      </c>
+      <c r="T101" s="20" t="n">
+        <v>923</v>
       </c>
       <c r="U101" s="20" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="V101" s="20" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="W101" s="20" t="n">
-        <v>0</v>
+        <v>-165</v>
+      </c>
+      <c r="X101" s="20" t="n">
+        <v>1667</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>상각채권 추심이익</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D102" s="20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E102" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F102" s="20" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G102" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H102" s="20" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L102" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M102" s="20" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="N102" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="T102" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U102" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="V102" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W102" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X102" s="20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C103" s="20" t="n">
-        <v>54</v>
+        <v>1270</v>
       </c>
       <c r="D103" s="20" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>34</v>
+        <v>1250</v>
       </c>
       <c r="G103" s="20" t="n">
-        <v>0</v>
+        <v>-117</v>
       </c>
       <c r="H103" s="20" t="n">
-        <v>73</v>
+        <v>1300</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="L103" s="20" t="n">
-        <v>0</v>
+        <v>1861</v>
       </c>
       <c r="M103" s="20" t="n">
-        <v>0</v>
+        <v>2469</v>
+      </c>
+      <c r="N103" s="20" t="n">
+        <v>2622</v>
+      </c>
+      <c r="T103" s="20" t="n">
+        <v>1070</v>
       </c>
       <c r="U103" s="20" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="V103" s="20" t="n">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="W103" s="20" t="n">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="X103" s="20" t="n">
-        <v>0</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="18" t="inlineStr">
-        <is>
-          <t>대손충당금 전입</t>
-        </is>
-      </c>
-      <c r="C104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="20" t="n">
-        <v>-51</v>
-      </c>
-      <c r="F104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="20" t="n">
-        <v>-51</v>
-      </c>
-      <c r="W104" s="20" t="n">
-        <v>0</v>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>1073</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>1717</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>2072</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>3480</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>816</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>1009</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>1709</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>5288</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>3408</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>2917</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>19741</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>656</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>1717</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>1009</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>2917</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="18" t="inlineStr">
-        <is>
-          <t>재고자산 평가손실</t>
-        </is>
-      </c>
-      <c r="C105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="20" t="n">
-        <v>0</v>
+      <c r="A105" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G105" s="15">
+        <f>IF(OR(G104="",C104=""),"",IF(C104&lt;=0,"",IFERROR(G104/C104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H105" s="15">
+        <f>IF(OR(H104="",D104=""),"",IF(D104&lt;=0,"",IFERROR(H104/D104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I105" s="15">
+        <f>IF(OR(I104="",E104=""),"",IF(E104&lt;=0,"",IFERROR(I104/E104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J105" s="15">
+        <f>IF(OR(J104="",F104=""),"",IF(F104&lt;=0,"",IFERROR(J104/F104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K105" s="15">
+        <f>IF(OR(K104="",G104=""),"",IF(G104&lt;=0,"",IFERROR(K104/G104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L105" s="15">
+        <f>IF(OR(L104="",H104=""),"",IF(H104&lt;=0,"",IFERROR(L104/H104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M105" s="15">
+        <f>IF(OR(M104="",I104=""),"",IF(I104&lt;=0,"",IFERROR(M104/I104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N105" s="15">
+        <f>IF(OR(N104="",J104=""),"",IF(J104&lt;=0,"",IFERROR(N104/J104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T105" s="15">
+        <f>IF(OR(T104="",S104=""),"",IF(S104&lt;=0,"",IFERROR(T104/S104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U105" s="15">
+        <f>IF(OR(U104="",T104=""),"",IF(T104&lt;=0,"",IFERROR(U104/T104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V105" s="15">
+        <f>IF(OR(V104="",U104=""),"",IF(U104&lt;=0,"",IFERROR(V104/U104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W105" s="15">
+        <f>IF(OR(W104="",V104=""),"",IF(V104&lt;=0,"",IFERROR(W104/V104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X105" s="15">
+        <f>IF(OR(X104="",W104=""),"",IF(W104&lt;=0,"",IFERROR(X104/W104-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
+          <t>투자유가증권 매각이익</t>
         </is>
       </c>
       <c r="C106" s="20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D106" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E106" s="20" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="F106" s="20" t="n">
         <v>0</v>
@@ -7444,3189 +7575,3949 @@
         <v>0</v>
       </c>
       <c r="V106" s="20" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="W106" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>1369</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>1072</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>1768</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>2107</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>3479</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>890</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>1008</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>1709</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>5288</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>3408</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>2917</v>
-      </c>
-      <c r="N107" s="12" t="n">
-        <v>19741</v>
-      </c>
-      <c r="T107" s="12" t="n">
-        <v>656</v>
-      </c>
-      <c r="U107" s="12" t="n">
-        <v>728</v>
-      </c>
-      <c r="V107" s="12" t="n">
-        <v>1768</v>
-      </c>
-      <c r="W107" s="12" t="n">
-        <v>1008</v>
-      </c>
-      <c r="X107" s="12" t="n">
-        <v>2917</v>
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>상각채권 추심이익</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="G107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="I107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="D108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="G108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>대손충당금 전입</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="20" t="n">
+        <v>-51</v>
+      </c>
+      <c r="F109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="20" t="n">
+        <v>-51</v>
+      </c>
+      <c r="W109" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>재고자산 평가손실</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="20" t="n">
+        <v>-52</v>
+      </c>
+      <c r="F111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="20" t="n">
+        <v>-52</v>
+      </c>
+      <c r="W111" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>1369</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>1072</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>1768</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>3479</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>890</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>1008</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>1709</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>5288</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>3408</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>2917</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>19741</v>
+      </c>
+      <c r="T112" s="12" t="n">
+        <v>656</v>
+      </c>
+      <c r="U112" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>1768</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>1008</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
           <t>법인세 등</t>
         </is>
       </c>
-      <c r="C108" s="20" t="n">
+      <c r="C113" s="20" t="n">
         <v>319</v>
       </c>
-      <c r="D108" s="20" t="n">
+      <c r="D113" s="20" t="n">
         <v>281</v>
       </c>
-      <c r="E108" s="20" t="n">
+      <c r="E113" s="20" t="n">
         <v>459</v>
       </c>
-      <c r="F108" s="20" t="n">
+      <c r="F113" s="20" t="n">
         <v>567</v>
       </c>
-      <c r="G108" s="20" t="n">
+      <c r="G113" s="20" t="n">
         <v>995</v>
       </c>
-      <c r="H108" s="20" t="n">
+      <c r="H113" s="20" t="n">
         <v>159</v>
       </c>
-      <c r="I108" s="20" t="n">
+      <c r="I113" s="20" t="n">
         <v>175</v>
       </c>
-      <c r="J108" s="20" t="n">
+      <c r="J113" s="20" t="n">
         <v>438</v>
       </c>
-      <c r="K108" s="20" t="n">
+      <c r="K113" s="20" t="n">
         <v>1780</v>
       </c>
-      <c r="L108" s="20" t="n">
+      <c r="L113" s="20" t="n">
         <v>844</v>
       </c>
-      <c r="M108" s="20" t="n">
+      <c r="M113" s="20" t="n">
         <v>245</v>
       </c>
-      <c r="N108" s="20" t="n">
+      <c r="N113" s="20" t="n">
         <v>5221</v>
       </c>
-      <c r="T108" s="20" t="n">
+      <c r="T113" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="U108" s="20" t="n">
+      <c r="U113" s="20" t="n">
         <v>191</v>
       </c>
-      <c r="V108" s="20" t="n">
+      <c r="V113" s="20" t="n">
         <v>459</v>
       </c>
-      <c r="W108" s="20" t="n">
+      <c r="W113" s="20" t="n">
         <v>175</v>
       </c>
-      <c r="X108" s="20" t="n">
+      <c r="X113" s="20" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C109" s="12" t="n">
+      <c r="C114" s="12" t="n">
         <v>1048</v>
       </c>
-      <c r="D109" s="12" t="n">
+      <c r="D114" s="12" t="n">
         <v>792</v>
       </c>
-      <c r="E109" s="12" t="n">
+      <c r="E114" s="12" t="n">
         <v>1308</v>
       </c>
-      <c r="F109" s="12" t="n">
+      <c r="F114" s="12" t="n">
         <v>1539</v>
       </c>
-      <c r="G109" s="12" t="n">
+      <c r="G114" s="12" t="n">
         <v>2485</v>
       </c>
-      <c r="H109" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>730</v>
       </c>
-      <c r="I109" s="12" t="n">
+      <c r="I114" s="12" t="n">
         <v>834</v>
       </c>
-      <c r="J109" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>1270</v>
       </c>
-      <c r="K109" s="12" t="n">
+      <c r="K114" s="12" t="n">
         <v>3509</v>
       </c>
-      <c r="L109" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>2563</v>
       </c>
-      <c r="M109" s="12" t="n">
+      <c r="M114" s="12" t="n">
         <v>2673</v>
       </c>
-      <c r="N109" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>14520</v>
       </c>
-      <c r="T109" s="12" t="n">
+      <c r="T114" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="U109" s="12" t="n">
+      <c r="U114" s="12" t="n">
         <v>538</v>
       </c>
-      <c r="V109" s="12" t="n">
+      <c r="V114" s="12" t="n">
         <v>1308</v>
       </c>
-      <c r="W109" s="12" t="n">
+      <c r="W114" s="12" t="n">
         <v>834</v>
       </c>
-      <c r="X109" s="12" t="n">
+      <c r="X114" s="12" t="n">
         <v>2673</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G115" s="15">
+        <f>IF(OR(G114="",C114=""),"",IF(C114&lt;=0,"",IFERROR(G114/C114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H115" s="15">
+        <f>IF(OR(H114="",D114=""),"",IF(D114&lt;=0,"",IFERROR(H114/D114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I115" s="15">
+        <f>IF(OR(I114="",E114=""),"",IF(E114&lt;=0,"",IFERROR(I114/E114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J115" s="15">
+        <f>IF(OR(J114="",F114=""),"",IF(F114&lt;=0,"",IFERROR(J114/F114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K115" s="15">
+        <f>IF(OR(K114="",G114=""),"",IF(G114&lt;=0,"",IFERROR(K114/G114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L115" s="15">
+        <f>IF(OR(L114="",H114=""),"",IF(H114&lt;=0,"",IFERROR(L114/H114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M115" s="15">
+        <f>IF(OR(M114="",I114=""),"",IF(I114&lt;=0,"",IFERROR(M114/I114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N115" s="15">
+        <f>IF(OR(N114="",J114=""),"",IF(J114&lt;=0,"",IFERROR(N114/J114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T115" s="15">
+        <f>IF(OR(T114="",S114=""),"",IF(S114&lt;=0,"",IFERROR(T114/S114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U115" s="15">
+        <f>IF(OR(U114="",T114=""),"",IF(T114&lt;=0,"",IFERROR(U114/T114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V115" s="15">
+        <f>IF(OR(V114="",U114=""),"",IF(U114&lt;=0,"",IFERROR(V114/U114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W115" s="15">
+        <f>IF(OR(W114="",V114=""),"",IF(V114&lt;=0,"",IFERROR(W114/V114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X115" s="15">
+        <f>IF(OR(X114="",W114=""),"",IF(W114&lt;=0,"",IFERROR(X114/W114-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>비지배주주 순이익</t>
         </is>
       </c>
-      <c r="C110" s="12" t="n">
+      <c r="C116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="12" t="n">
+      <c r="D116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="E116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="12" t="n">
+      <c r="F116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="12" t="n">
+      <c r="G116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="12" t="n">
+      <c r="H116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="12" t="n">
+      <c r="I116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="T110" s="12" t="n">
+      <c r="T116" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="U110" s="12" t="n">
+      <c r="U116" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="V110" s="12" t="n">
+      <c r="V116" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W110" s="12" t="n">
+      <c r="W116" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="C111" s="12" t="n">
+      <c r="C117" s="12" t="n">
         <v>1048</v>
       </c>
-      <c r="D111" s="12" t="n">
+      <c r="D117" s="12" t="n">
         <v>791</v>
       </c>
-      <c r="E111" s="12" t="n">
+      <c r="E117" s="12" t="n">
         <v>1309</v>
       </c>
-      <c r="F111" s="12" t="n">
+      <c r="F117" s="12" t="n">
         <v>1539</v>
       </c>
-      <c r="G111" s="12" t="n">
+      <c r="G117" s="12" t="n">
         <v>2485</v>
       </c>
-      <c r="H111" s="12" t="n">
+      <c r="H117" s="12" t="n">
         <v>730</v>
       </c>
-      <c r="I111" s="12" t="n">
+      <c r="I117" s="12" t="n">
         <v>834</v>
       </c>
-      <c r="J111" s="12" t="n">
+      <c r="J117" s="12" t="n">
         <v>1270</v>
       </c>
-      <c r="K111" s="12" t="n">
+      <c r="K117" s="12" t="n">
         <v>3509</v>
       </c>
-      <c r="L111" s="12" t="n">
+      <c r="L117" s="12" t="n">
         <v>2563</v>
       </c>
-      <c r="M111" s="12" t="n">
+      <c r="M117" s="12" t="n">
         <v>2673</v>
       </c>
-      <c r="N111" s="12" t="n">
+      <c r="N117" s="12" t="n">
         <v>14520</v>
       </c>
-      <c r="T111" s="12" t="n">
+      <c r="T117" s="12" t="n">
         <v>559</v>
       </c>
-      <c r="U111" s="12" t="n">
+      <c r="U117" s="12" t="n">
         <v>537</v>
       </c>
-      <c r="V111" s="12" t="n">
+      <c r="V117" s="12" t="n">
         <v>1309</v>
       </c>
-      <c r="W111" s="12" t="n">
+      <c r="W117" s="12" t="n">
         <v>834</v>
       </c>
-      <c r="X111" s="12" t="n">
+      <c r="X117" s="12" t="n">
         <v>2673</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="16" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G118" s="15">
+        <f>IF(OR(G117="",C117=""),"",IF(C117&lt;=0,"",IFERROR(G117/C117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H118" s="15">
+        <f>IF(OR(H117="",D117=""),"",IF(D117&lt;=0,"",IFERROR(H117/D117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I118" s="15">
+        <f>IF(OR(I117="",E117=""),"",IF(E117&lt;=0,"",IFERROR(I117/E117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J118" s="15">
+        <f>IF(OR(J117="",F117=""),"",IF(F117&lt;=0,"",IFERROR(J117/F117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K118" s="15">
+        <f>IF(OR(K117="",G117=""),"",IF(G117&lt;=0,"",IFERROR(K117/G117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L118" s="15">
+        <f>IF(OR(L117="",H117=""),"",IF(H117&lt;=0,"",IFERROR(L117/H117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M118" s="15">
+        <f>IF(OR(M117="",I117=""),"",IF(I117&lt;=0,"",IFERROR(M117/I117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N118" s="15">
+        <f>IF(OR(N117="",J117=""),"",IF(J117&lt;=0,"",IFERROR(N117/J117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T118" s="15">
+        <f>IF(OR(T117="",S117=""),"",IF(S117&lt;=0,"",IFERROR(T117/S117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U118" s="15">
+        <f>IF(OR(U117="",T117=""),"",IF(T117&lt;=0,"",IFERROR(U117/T117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V118" s="15">
+        <f>IF(OR(V117="",U117=""),"",IF(U117&lt;=0,"",IFERROR(V117/U117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W118" s="15">
+        <f>IF(OR(W117="",V117=""),"",IF(V117&lt;=0,"",IFERROR(W117/V117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X118" s="15">
+        <f>IF(OR(X117="",W117=""),"",IF(W117&lt;=0,"",IFERROR(X117/W117-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B113" s="42" t="inlineStr">
+      <c r="B120" s="42" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C113" s="16" t="n"/>
-      <c r="D113" s="16" t="n"/>
-      <c r="E113" s="16" t="n"/>
-      <c r="F113" s="16" t="n"/>
-      <c r="G113" s="16" t="n"/>
-      <c r="H113" s="16" t="n"/>
-      <c r="I113" s="16" t="n"/>
-      <c r="J113" s="16" t="n"/>
-      <c r="K113" s="16" t="n"/>
-      <c r="L113" s="16" t="n"/>
-      <c r="M113" s="16" t="n"/>
-      <c r="N113" s="16" t="n"/>
-      <c r="O113" s="16" t="n"/>
-      <c r="P113" s="16" t="n"/>
-      <c r="Q113" s="16" t="n"/>
-      <c r="R113" s="16" t="n"/>
-      <c r="S113" s="16" t="n"/>
-      <c r="T113" s="16" t="n"/>
-      <c r="U113" s="16" t="n"/>
-      <c r="V113" s="16" t="n"/>
-      <c r="W113" s="16" t="n"/>
-      <c r="X113" s="16" t="n"/>
-      <c r="Y113" s="16" t="n"/>
-      <c r="Z113" s="16" t="n"/>
-      <c r="AA113" s="16" t="n"/>
-      <c r="AB113" s="16" t="n"/>
-      <c r="AC113" s="16" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="C120" s="16" t="n"/>
+      <c r="D120" s="16" t="n"/>
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="16" t="n"/>
+      <c r="G120" s="16" t="n"/>
+      <c r="H120" s="16" t="n"/>
+      <c r="I120" s="16" t="n"/>
+      <c r="J120" s="16" t="n"/>
+      <c r="K120" s="16" t="n"/>
+      <c r="L120" s="16" t="n"/>
+      <c r="M120" s="16" t="n"/>
+      <c r="N120" s="16" t="n"/>
+      <c r="O120" s="16" t="n"/>
+      <c r="P120" s="16" t="n"/>
+      <c r="Q120" s="16" t="n"/>
+      <c r="R120" s="16" t="n"/>
+      <c r="S120" s="16" t="n"/>
+      <c r="T120" s="16" t="n"/>
+      <c r="U120" s="16" t="n"/>
+      <c r="V120" s="16" t="n"/>
+      <c r="W120" s="16" t="n"/>
+      <c r="X120" s="16" t="n"/>
+      <c r="Y120" s="16" t="n"/>
+      <c r="Z120" s="16" t="n"/>
+      <c r="AA120" s="16" t="n"/>
+      <c r="AB120" s="16" t="n"/>
+      <c r="AC120" s="16" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B121" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C121" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E121" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F121" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="H121" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I121" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J114" s="5" t="inlineStr">
+      <c r="J121" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K114" s="5" t="inlineStr">
+      <c r="K121" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="L121" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M114" s="5" t="inlineStr">
+      <c r="M121" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N114" s="5" t="inlineStr">
+      <c r="N121" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O114" s="5" t="inlineStr">
+      <c r="O121" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P114" s="5" t="inlineStr">
+      <c r="P121" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q114" s="5" t="inlineStr">
+      <c r="Q121" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R114" s="5" t="inlineStr">
+      <c r="R121" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S114" s="5" t="inlineStr">
+      <c r="S121" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T114" s="5" t="inlineStr">
+      <c r="T121" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U114" s="5" t="inlineStr">
+      <c r="U121" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V114" s="5" t="inlineStr">
+      <c r="V121" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W114" s="5" t="inlineStr">
+      <c r="W121" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X114" s="5" t="inlineStr">
+      <c r="X121" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y114" s="5" t="inlineStr">
+      <c r="Y121" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z114" s="5" t="inlineStr">
+      <c r="Z121" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA114" s="5" t="inlineStr">
+      <c r="AA121" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB114" s="5" t="inlineStr">
+      <c r="AB121" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC114" s="5" t="inlineStr">
+      <c r="AC121" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="n">
-        <v>1048</v>
-      </c>
-      <c r="D115" s="12" t="n">
-        <v>792</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>1308</v>
-      </c>
-      <c r="F115" s="12" t="n">
-        <v>1539</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>2485</v>
-      </c>
-      <c r="H115" s="12" t="n">
-        <v>730</v>
-      </c>
-      <c r="I115" s="12" t="n">
-        <v>834</v>
-      </c>
-      <c r="J115" s="12" t="n">
-        <v>1270</v>
-      </c>
-      <c r="K115" s="12" t="n">
-        <v>3509</v>
-      </c>
-      <c r="L115" s="12" t="n">
-        <v>2563</v>
-      </c>
-      <c r="M115" s="12" t="n">
-        <v>2673</v>
-      </c>
-      <c r="N115" s="12" t="n">
-        <v>14520</v>
-      </c>
-      <c r="T115" s="12" t="n">
-        <v>600</v>
-      </c>
-      <c r="U115" s="12" t="n">
-        <v>538</v>
-      </c>
-      <c r="V115" s="12" t="n">
-        <v>1308</v>
-      </c>
-      <c r="W115" s="12" t="n">
-        <v>834</v>
-      </c>
-      <c r="X115" s="12" t="n">
-        <v>2673</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C116" s="20" t="n">
-        <v>-38</v>
-      </c>
-      <c r="D116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="20" t="n">
-        <v>-53</v>
-      </c>
-      <c r="U116" s="20" t="n">
-        <v>70</v>
-      </c>
-      <c r="V116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
-        <is>
-          <t>이연헤지손익</t>
-        </is>
-      </c>
-      <c r="C117" s="20" t="n">
-        <v>177</v>
-      </c>
-      <c r="D117" s="20" t="n">
-        <v>120</v>
-      </c>
-      <c r="E117" s="20" t="n">
-        <v>-178</v>
-      </c>
-      <c r="F117" s="20" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G117" s="20" t="n">
-        <v>315</v>
-      </c>
-      <c r="H117" s="20" t="n">
-        <v>-398</v>
-      </c>
-      <c r="I117" s="20" t="n">
-        <v>427</v>
-      </c>
-      <c r="J117" s="20" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K117" s="20" t="n">
-        <v>-345</v>
-      </c>
-      <c r="L117" s="20" t="n">
-        <v>-209</v>
-      </c>
-      <c r="M117" s="20" t="n">
-        <v>-65</v>
-      </c>
-      <c r="N117" s="20" t="n">
-        <v>-293</v>
-      </c>
-      <c r="T117" s="20" t="n">
-        <v>-53</v>
-      </c>
-      <c r="U117" s="20" t="n">
-        <v>-22</v>
-      </c>
-      <c r="V117" s="20" t="n">
-        <v>-178</v>
-      </c>
-      <c r="W117" s="20" t="n">
-        <v>427</v>
-      </c>
-      <c r="X117" s="20" t="n">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="n">
-        <v>715</v>
-      </c>
-      <c r="D118" s="20" t="n">
-        <v>-1212</v>
-      </c>
-      <c r="E118" s="20" t="n">
-        <v>1537</v>
-      </c>
-      <c r="F118" s="20" t="n">
-        <v>1612</v>
-      </c>
-      <c r="G118" s="20" t="n">
-        <v>-3092</v>
-      </c>
-      <c r="H118" s="20" t="n">
-        <v>2687</v>
-      </c>
-      <c r="I118" s="20" t="n">
-        <v>-1534</v>
-      </c>
-      <c r="J118" s="20" t="n">
-        <v>-863</v>
-      </c>
-      <c r="K118" s="20" t="n">
-        <v>784</v>
-      </c>
-      <c r="L118" s="20" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M118" s="20" t="n">
-        <v>799</v>
-      </c>
-      <c r="N118" s="20" t="n">
-        <v>721</v>
-      </c>
-      <c r="T118" s="20" t="n">
-        <v>932</v>
-      </c>
-      <c r="U118" s="20" t="n">
-        <v>128</v>
-      </c>
-      <c r="V118" s="20" t="n">
-        <v>1537</v>
-      </c>
-      <c r="W118" s="20" t="n">
-        <v>-1534</v>
-      </c>
-      <c r="X118" s="20" t="n">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="18" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C119" s="20" t="n">
-        <v>854</v>
-      </c>
-      <c r="D119" s="20" t="n">
-        <v>-1092</v>
-      </c>
-      <c r="E119" s="20" t="n">
-        <v>1359</v>
-      </c>
-      <c r="F119" s="20" t="n">
-        <v>1480</v>
-      </c>
-      <c r="G119" s="20" t="n">
-        <v>-2776</v>
-      </c>
-      <c r="H119" s="20" t="n">
-        <v>2288</v>
-      </c>
-      <c r="I119" s="20" t="n">
-        <v>-1107</v>
-      </c>
-      <c r="J119" s="20" t="n">
-        <v>-873</v>
-      </c>
-      <c r="K119" s="20" t="n">
-        <v>439</v>
-      </c>
-      <c r="L119" s="20" t="n">
-        <v>1340</v>
-      </c>
-      <c r="M119" s="20" t="n">
-        <v>735</v>
-      </c>
-      <c r="N119" s="20" t="n">
-        <v>427</v>
-      </c>
-      <c r="T119" s="20" t="n">
-        <v>827</v>
-      </c>
-      <c r="U119" s="20" t="n">
-        <v>178</v>
-      </c>
-      <c r="V119" s="20" t="n">
-        <v>1359</v>
-      </c>
-      <c r="W119" s="20" t="n">
-        <v>-1107</v>
-      </c>
-      <c r="X119" s="20" t="n">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="n">
-        <v>1904</v>
-      </c>
-      <c r="D120" s="12" t="n">
-        <v>-301</v>
-      </c>
-      <c r="E120" s="12" t="n">
-        <v>2668</v>
-      </c>
-      <c r="F120" s="12" t="n">
-        <v>3020</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>-293</v>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>3019</v>
-      </c>
-      <c r="I120" s="12" t="n">
-        <v>-273</v>
-      </c>
-      <c r="J120" s="12" t="n">
-        <v>396</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>3949</v>
-      </c>
-      <c r="L120" s="12" t="n">
-        <v>3904</v>
-      </c>
-      <c r="M120" s="12" t="n">
-        <v>3408</v>
-      </c>
-      <c r="N120" s="12" t="n">
-        <v>14947</v>
-      </c>
-      <c r="T120" s="12" t="n">
-        <v>1427</v>
-      </c>
-      <c r="U120" s="12" t="n">
-        <v>715</v>
-      </c>
-      <c r="V120" s="12" t="n">
-        <v>2668</v>
-      </c>
-      <c r="W120" s="12" t="n">
-        <v>-273</v>
-      </c>
-      <c r="X120" s="12" t="n">
-        <v>3408</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="n">
-        <v>1904</v>
-      </c>
-      <c r="D121" s="12" t="n">
-        <v>-301</v>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v>2668</v>
-      </c>
-      <c r="F121" s="12" t="n">
-        <v>3020</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>-293</v>
-      </c>
-      <c r="H121" s="12" t="n">
-        <v>3019</v>
-      </c>
-      <c r="I121" s="12" t="n">
-        <v>-273</v>
-      </c>
-      <c r="J121" s="12" t="n">
-        <v>396</v>
-      </c>
-      <c r="K121" s="12" t="n">
-        <v>3949</v>
-      </c>
-      <c r="L121" s="12" t="n">
-        <v>3904</v>
-      </c>
-      <c r="M121" s="12" t="n">
-        <v>3408</v>
-      </c>
-      <c r="N121" s="12" t="n">
-        <v>14947</v>
-      </c>
-      <c r="T121" s="12" t="n">
-        <v>1340</v>
-      </c>
-      <c r="U121" s="12" t="n">
-        <v>708</v>
-      </c>
-      <c r="V121" s="12" t="n">
-        <v>2668</v>
-      </c>
-      <c r="W121" s="12" t="n">
-        <v>-273</v>
-      </c>
-      <c r="X121" s="12" t="n">
-        <v>3408</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>비지배주주 포괄이익</t>
+          <t>순이익</t>
         </is>
       </c>
       <c r="C122" s="12" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>792</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>1539</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>2485</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>730</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>834</v>
+      </c>
+      <c r="J122" s="12" t="n">
+        <v>1270</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>3509</v>
+      </c>
+      <c r="L122" s="12" t="n">
+        <v>2563</v>
+      </c>
+      <c r="M122" s="12" t="n">
+        <v>2673</v>
+      </c>
+      <c r="N122" s="12" t="n">
+        <v>14520</v>
+      </c>
+      <c r="T122" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="U122" s="12" t="n">
+        <v>538</v>
+      </c>
+      <c r="V122" s="12" t="n">
+        <v>1308</v>
+      </c>
+      <c r="W122" s="12" t="n">
+        <v>834</v>
+      </c>
+      <c r="X122" s="12" t="n">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="n">
+        <v>-38</v>
+      </c>
+      <c r="D123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="E123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="F123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="G123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="H123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="I123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="T123" s="20" t="n">
+        <v>-53</v>
+      </c>
+      <c r="U123" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="V123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="U122" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="V122" s="12" t="n">
+      <c r="W123" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="W122" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124">
-      <c r="A124" s="16" t="inlineStr">
-        <is>
-          <t>부문 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B124" s="42" t="inlineStr">
-        <is>
-          <t>부문 · 항목</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="n"/>
-      <c r="D124" s="16" t="n"/>
-      <c r="E124" s="16" t="n"/>
-      <c r="F124" s="16" t="n"/>
-      <c r="G124" s="16" t="n"/>
-      <c r="H124" s="16" t="n"/>
-      <c r="I124" s="16" t="n"/>
-      <c r="J124" s="16" t="n"/>
-      <c r="K124" s="16" t="n"/>
-      <c r="L124" s="16" t="n"/>
-      <c r="M124" s="16" t="n"/>
-      <c r="N124" s="16" t="n"/>
-      <c r="O124" s="16" t="n"/>
-      <c r="P124" s="16" t="n"/>
-      <c r="Q124" s="16" t="n"/>
-      <c r="R124" s="16" t="n"/>
-      <c r="S124" s="16" t="n"/>
-      <c r="T124" s="16" t="n"/>
-      <c r="U124" s="16" t="n"/>
-      <c r="V124" s="16" t="n"/>
-      <c r="W124" s="16" t="n"/>
-      <c r="X124" s="16" t="n"/>
-      <c r="Y124" s="16" t="n"/>
-      <c r="Z124" s="16" t="n"/>
-      <c r="AA124" s="16" t="n"/>
-      <c r="AB124" s="16" t="n"/>
-      <c r="AC124" s="16" t="n"/>
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>이연헤지손익</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="n">
+        <v>177</v>
+      </c>
+      <c r="D124" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="E124" s="20" t="n">
+        <v>-178</v>
+      </c>
+      <c r="F124" s="20" t="n">
+        <v>-132</v>
+      </c>
+      <c r="G124" s="20" t="n">
+        <v>315</v>
+      </c>
+      <c r="H124" s="20" t="n">
+        <v>-398</v>
+      </c>
+      <c r="I124" s="20" t="n">
+        <v>427</v>
+      </c>
+      <c r="J124" s="20" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K124" s="20" t="n">
+        <v>-345</v>
+      </c>
+      <c r="L124" s="20" t="n">
+        <v>-209</v>
+      </c>
+      <c r="M124" s="20" t="n">
+        <v>-65</v>
+      </c>
+      <c r="N124" s="20" t="n">
+        <v>-293</v>
+      </c>
+      <c r="T124" s="20" t="n">
+        <v>-53</v>
+      </c>
+      <c r="U124" s="20" t="n">
+        <v>-22</v>
+      </c>
+      <c r="V124" s="20" t="n">
+        <v>-178</v>
+      </c>
+      <c r="W124" s="20" t="n">
+        <v>427</v>
+      </c>
+      <c r="X124" s="20" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M125" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N125" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O125" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P125" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q125" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R125" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S125" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T125" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U125" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V125" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W125" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X125" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y125" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z125" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA125" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB125" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC125" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A125" s="18" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="n">
+        <v>715</v>
+      </c>
+      <c r="D125" s="20" t="n">
+        <v>-1212</v>
+      </c>
+      <c r="E125" s="20" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F125" s="20" t="n">
+        <v>1612</v>
+      </c>
+      <c r="G125" s="20" t="n">
+        <v>-3092</v>
+      </c>
+      <c r="H125" s="20" t="n">
+        <v>2687</v>
+      </c>
+      <c r="I125" s="20" t="n">
+        <v>-1534</v>
+      </c>
+      <c r="J125" s="20" t="n">
+        <v>-863</v>
+      </c>
+      <c r="K125" s="20" t="n">
+        <v>784</v>
+      </c>
+      <c r="L125" s="20" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M125" s="20" t="n">
+        <v>799</v>
+      </c>
+      <c r="N125" s="20" t="n">
+        <v>721</v>
+      </c>
+      <c r="T125" s="20" t="n">
+        <v>932</v>
+      </c>
+      <c r="U125" s="20" t="n">
+        <v>128</v>
+      </c>
+      <c r="V125" s="20" t="n">
+        <v>1537</v>
+      </c>
+      <c r="W125" s="20" t="n">
+        <v>-1534</v>
+      </c>
+      <c r="X125" s="20" t="n">
+        <v>799</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>일본 · 외부 고객 매출</t>
-        </is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="n">
+        <v>854</v>
+      </c>
+      <c r="D126" s="20" t="n">
+        <v>-1092</v>
       </c>
       <c r="E126" s="20" t="n">
-        <v>29561</v>
+        <v>1359</v>
       </c>
       <c r="F126" s="20" t="n">
-        <v>30324</v>
+        <v>1480</v>
+      </c>
+      <c r="G126" s="20" t="n">
+        <v>-2776</v>
+      </c>
+      <c r="H126" s="20" t="n">
+        <v>2288</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>30224</v>
+        <v>-1107</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>27340</v>
+        <v>-873</v>
+      </c>
+      <c r="K126" s="20" t="n">
+        <v>439</v>
+      </c>
+      <c r="L126" s="20" t="n">
+        <v>1340</v>
       </c>
       <c r="M126" s="20" t="n">
-        <v>51111</v>
+        <v>735</v>
       </c>
       <c r="N126" s="20" t="n">
-        <v>132595</v>
+        <v>427</v>
+      </c>
+      <c r="T126" s="20" t="n">
+        <v>827</v>
+      </c>
+      <c r="U126" s="20" t="n">
+        <v>178</v>
       </c>
       <c r="V126" s="20" t="n">
-        <v>29561</v>
+        <v>1359</v>
       </c>
       <c r="W126" s="20" t="n">
-        <v>30224</v>
+        <v>-1107</v>
       </c>
       <c r="X126" s="20" t="n">
-        <v>51111</v>
+        <v>735</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="18" t="inlineStr">
-        <is>
-          <t>해외 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="E127" s="20" t="n">
-        <v>73621</v>
-      </c>
-      <c r="F127" s="20" t="n">
-        <v>72562</v>
-      </c>
-      <c r="I127" s="20" t="n">
-        <v>83935</v>
-      </c>
-      <c r="J127" s="20" t="n">
-        <v>75046</v>
-      </c>
-      <c r="M127" s="20" t="n">
-        <v>188211</v>
-      </c>
-      <c r="N127" s="20" t="n">
-        <v>262983</v>
-      </c>
-      <c r="V127" s="20" t="n">
-        <v>73621</v>
-      </c>
-      <c r="W127" s="20" t="n">
-        <v>83935</v>
-      </c>
-      <c r="X127" s="20" t="n">
-        <v>188211</v>
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D127" s="12" t="n">
+        <v>-301</v>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>3020</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>-293</v>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>3019</v>
+      </c>
+      <c r="I127" s="12" t="n">
+        <v>-273</v>
+      </c>
+      <c r="J127" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>3949</v>
+      </c>
+      <c r="L127" s="12" t="n">
+        <v>3904</v>
+      </c>
+      <c r="M127" s="12" t="n">
+        <v>3408</v>
+      </c>
+      <c r="N127" s="12" t="n">
+        <v>14947</v>
+      </c>
+      <c r="T127" s="12" t="n">
+        <v>1427</v>
+      </c>
+      <c r="U127" s="12" t="n">
+        <v>715</v>
+      </c>
+      <c r="V127" s="12" t="n">
+        <v>2668</v>
+      </c>
+      <c r="W127" s="12" t="n">
+        <v>-273</v>
+      </c>
+      <c r="X127" s="12" t="n">
+        <v>3408</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="F128" s="20" t="n">
-        <v>102886</v>
-      </c>
-      <c r="J128" s="20" t="n">
-        <v>102386</v>
-      </c>
-      <c r="N128" s="20" t="n">
-        <v>395578</v>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D128" s="12" t="n">
+        <v>-301</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>3020</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>-293</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>3019</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>-273</v>
+      </c>
+      <c r="J128" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="K128" s="12" t="n">
+        <v>3949</v>
+      </c>
+      <c r="L128" s="12" t="n">
+        <v>3904</v>
+      </c>
+      <c r="M128" s="12" t="n">
+        <v>3408</v>
+      </c>
+      <c r="N128" s="12" t="n">
+        <v>14947</v>
+      </c>
+      <c r="T128" s="12" t="n">
+        <v>1340</v>
+      </c>
+      <c r="U128" s="12" t="n">
+        <v>708</v>
+      </c>
+      <c r="V128" s="12" t="n">
+        <v>2668</v>
+      </c>
+      <c r="W128" s="12" t="n">
+        <v>-273</v>
+      </c>
+      <c r="X128" s="12" t="n">
+        <v>3408</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="18" t="inlineStr">
-        <is>
-          <t>일본 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="E129" s="20" t="n">
-        <v>8938</v>
-      </c>
-      <c r="F129" s="20" t="n">
-        <v>14003</v>
-      </c>
-      <c r="I129" s="20" t="n">
-        <v>9473</v>
-      </c>
-      <c r="J129" s="20" t="n">
-        <v>10818</v>
-      </c>
-      <c r="M129" s="20" t="n">
-        <v>17147</v>
-      </c>
-      <c r="N129" s="20" t="n">
-        <v>38742</v>
-      </c>
-      <c r="V129" s="20" t="n">
-        <v>8938</v>
-      </c>
-      <c r="W129" s="20" t="n">
-        <v>9473</v>
-      </c>
-      <c r="X129" s="20" t="n">
-        <v>17147</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="18" t="inlineStr">
-        <is>
-          <t>해외 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="E130" s="20" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F130" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I130" s="20" t="n">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>비지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="M130" s="20" t="n">
+      <c r="D129" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N130" s="20" t="n">
+      <c r="E129" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="20" t="n">
-        <v>1209</v>
-      </c>
-      <c r="W130" s="20" t="n">
+      <c r="F129" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="20" t="n">
+      <c r="G129" s="12" t="n">
         <v>0</v>
       </c>
+      <c r="H129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="U129" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="F131" s="20" t="n">
-        <v>14006</v>
-      </c>
-      <c r="J131" s="20" t="n">
-        <v>10849</v>
-      </c>
-      <c r="N131" s="20" t="n">
-        <v>38742</v>
-      </c>
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>부문 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B131" s="42" t="inlineStr">
+        <is>
+          <t>부문 · 항목</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="n"/>
+      <c r="D131" s="16" t="n"/>
+      <c r="E131" s="16" t="n"/>
+      <c r="F131" s="16" t="n"/>
+      <c r="G131" s="16" t="n"/>
+      <c r="H131" s="16" t="n"/>
+      <c r="I131" s="16" t="n"/>
+      <c r="J131" s="16" t="n"/>
+      <c r="K131" s="16" t="n"/>
+      <c r="L131" s="16" t="n"/>
+      <c r="M131" s="16" t="n"/>
+      <c r="N131" s="16" t="n"/>
+      <c r="O131" s="16" t="n"/>
+      <c r="P131" s="16" t="n"/>
+      <c r="Q131" s="16" t="n"/>
+      <c r="R131" s="16" t="n"/>
+      <c r="S131" s="16" t="n"/>
+      <c r="T131" s="16" t="n"/>
+      <c r="U131" s="16" t="n"/>
+      <c r="V131" s="16" t="n"/>
+      <c r="W131" s="16" t="n"/>
+      <c r="X131" s="16" t="n"/>
+      <c r="Y131" s="16" t="n"/>
+      <c r="Z131" s="16" t="n"/>
+      <c r="AA131" s="16" t="n"/>
+      <c r="AB131" s="16" t="n"/>
+      <c r="AC131" s="16" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="18" t="inlineStr">
-        <is>
-          <t>일본 · 계</t>
-        </is>
-      </c>
-      <c r="E132" s="20" t="n">
-        <v>38500</v>
-      </c>
-      <c r="F132" s="20" t="n">
-        <v>44327</v>
-      </c>
-      <c r="I132" s="20" t="n">
-        <v>39697</v>
-      </c>
-      <c r="J132" s="20" t="n">
-        <v>38159</v>
-      </c>
-      <c r="M132" s="20" t="n">
-        <v>68259</v>
-      </c>
-      <c r="N132" s="20" t="n">
-        <v>171337</v>
-      </c>
-      <c r="V132" s="20" t="n">
-        <v>38500</v>
-      </c>
-      <c r="W132" s="20" t="n">
-        <v>39697</v>
-      </c>
-      <c r="X132" s="20" t="n">
-        <v>68259</v>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O132" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P132" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q132" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R132" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S132" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T132" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U132" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V132" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W132" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X132" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y132" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z132" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA132" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB132" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC132" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>해외 · 계</t>
+          <t>일본 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="E133" s="20" t="n">
-        <v>74830</v>
+        <v>29561</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>72565</v>
+        <v>30324</v>
       </c>
       <c r="I133" s="20" t="n">
-        <v>83935</v>
+        <v>30224</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>75076</v>
+        <v>27340</v>
       </c>
       <c r="M133" s="20" t="n">
-        <v>188210</v>
+        <v>51111</v>
       </c>
       <c r="N133" s="20" t="n">
-        <v>262983</v>
+        <v>132595</v>
       </c>
       <c r="V133" s="20" t="n">
-        <v>74830</v>
+        <v>29561</v>
       </c>
       <c r="W133" s="20" t="n">
-        <v>83935</v>
+        <v>30224</v>
       </c>
       <c r="X133" s="20" t="n">
-        <v>188210</v>
+        <v>51111</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · 계</t>
-        </is>
-      </c>
-      <c r="F134" s="20" t="n">
-        <v>116893</v>
-      </c>
-      <c r="J134" s="20" t="n">
-        <v>113236</v>
-      </c>
-      <c r="N134" s="20" t="n">
-        <v>434321</v>
+      <c r="A134" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I134" s="15">
+        <f>IF(OR(I133="",E133=""),"",IF(E133&lt;=0,"",IFERROR(I133/E133-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J134" s="15">
+        <f>IF(OR(J133="",F133=""),"",IF(F133&lt;=0,"",IFERROR(J133/F133-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M134" s="15">
+        <f>IF(OR(M133="",I133=""),"",IF(I133&lt;=0,"",IFERROR(M133/I133-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N134" s="15">
+        <f>IF(OR(N133="",J133=""),"",IF(J133&lt;=0,"",IFERROR(N133/J133-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V134" s="15">
+        <f>IF(OR(V133="",U133=""),"",IF(U133&lt;=0,"",IFERROR(V133/U133-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W134" s="15">
+        <f>IF(OR(W133="",V133=""),"",IF(V133&lt;=0,"",IFERROR(W133/V133-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X134" s="15">
+        <f>IF(OR(X133="",W133=""),"",IF(W133&lt;=0,"",IFERROR(X133/W133-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>일본 · 부문 이익</t>
+          <t>해외 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="E135" s="20" t="n">
-        <v>740</v>
+        <v>73621</v>
       </c>
       <c r="F135" s="20" t="n">
-        <v>2052</v>
+        <v>72562</v>
       </c>
       <c r="I135" s="20" t="n">
-        <v>-159</v>
+        <v>83935</v>
       </c>
       <c r="J135" s="20" t="n">
-        <v>654</v>
+        <v>75046</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>66</v>
+        <v>188211</v>
       </c>
       <c r="N135" s="20" t="n">
-        <v>12782</v>
+        <v>262983</v>
       </c>
       <c r="V135" s="20" t="n">
-        <v>740</v>
+        <v>73621</v>
       </c>
       <c r="W135" s="20" t="n">
-        <v>-159</v>
+        <v>83935</v>
       </c>
       <c r="X135" s="20" t="n">
-        <v>66</v>
+        <v>188211</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="18" t="inlineStr">
-        <is>
-          <t>해외 · 부문 이익</t>
-        </is>
-      </c>
-      <c r="E136" s="20" t="n">
-        <v>1510</v>
-      </c>
-      <c r="F136" s="20" t="n">
-        <v>1185</v>
-      </c>
-      <c r="I136" s="20" t="n">
-        <v>1687</v>
-      </c>
-      <c r="J136" s="20" t="n">
-        <v>1252</v>
-      </c>
-      <c r="M136" s="20" t="n">
-        <v>5129</v>
-      </c>
-      <c r="N136" s="20" t="n">
-        <v>9583</v>
-      </c>
-      <c r="V136" s="20" t="n">
-        <v>1510</v>
-      </c>
-      <c r="W136" s="20" t="n">
-        <v>1687</v>
-      </c>
-      <c r="X136" s="20" t="n">
-        <v>5129</v>
+      <c r="A136" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I136" s="15">
+        <f>IF(OR(I135="",E135=""),"",IF(E135&lt;=0,"",IFERROR(I135/E135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J136" s="15">
+        <f>IF(OR(J135="",F135=""),"",IF(F135&lt;=0,"",IFERROR(J135/F135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M136" s="15">
+        <f>IF(OR(M135="",I135=""),"",IF(I135&lt;=0,"",IFERROR(M135/I135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N136" s="15">
+        <f>IF(OR(N135="",J135=""),"",IF(J135&lt;=0,"",IFERROR(N135/J135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V136" s="15">
+        <f>IF(OR(V135="",U135=""),"",IF(U135&lt;=0,"",IFERROR(V135/U135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W136" s="15">
+        <f>IF(OR(W135="",V135=""),"",IF(V135&lt;=0,"",IFERROR(W135/V135-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X136" s="15">
+        <f>IF(OR(X135="",W135=""),"",IF(W135&lt;=0,"",IFERROR(X135/W135-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 부문 이익</t>
+          <t>보고부문 합계 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="F137" s="20" t="n">
-        <v>3237</v>
+        <v>102886</v>
       </c>
       <c r="J137" s="20" t="n">
-        <v>1907</v>
+        <v>102386</v>
       </c>
       <c r="N137" s="20" t="n">
-        <v>22366</v>
+        <v>395578</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="J138" s="15">
+        <f>IF(OR(J137="",F137=""),"",IF(F137&lt;=0,"",IFERROR(J137/F137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N138" s="15">
+        <f>IF(OR(N137="",J137=""),"",IF(J137&lt;=0,"",IFERROR(N137/J137-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="16" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B139" s="42" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C139" s="16" t="n"/>
-      <c r="D139" s="16" t="n"/>
-      <c r="E139" s="16" t="n"/>
-      <c r="F139" s="16" t="n"/>
-      <c r="G139" s="16" t="n"/>
-      <c r="H139" s="16" t="n"/>
-      <c r="I139" s="16" t="n"/>
-      <c r="J139" s="16" t="n"/>
-      <c r="K139" s="16" t="n"/>
-      <c r="L139" s="16" t="n"/>
-      <c r="M139" s="16" t="n"/>
-      <c r="N139" s="16" t="n"/>
-      <c r="O139" s="16" t="n"/>
-      <c r="P139" s="16" t="n"/>
-      <c r="Q139" s="16" t="n"/>
-      <c r="R139" s="16" t="n"/>
-      <c r="S139" s="16" t="n"/>
-      <c r="T139" s="16" t="n"/>
-      <c r="U139" s="16" t="n"/>
-      <c r="V139" s="16" t="n"/>
-      <c r="W139" s="16" t="n"/>
-      <c r="X139" s="16" t="n"/>
-      <c r="Y139" s="16" t="n"/>
-      <c r="Z139" s="16" t="n"/>
-      <c r="AA139" s="16" t="n"/>
-      <c r="AB139" s="16" t="n"/>
-      <c r="AC139" s="16" t="n"/>
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>일본 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="n">
+        <v>8938</v>
+      </c>
+      <c r="F139" s="20" t="n">
+        <v>14003</v>
+      </c>
+      <c r="I139" s="20" t="n">
+        <v>9473</v>
+      </c>
+      <c r="J139" s="20" t="n">
+        <v>10818</v>
+      </c>
+      <c r="M139" s="20" t="n">
+        <v>17147</v>
+      </c>
+      <c r="N139" s="20" t="n">
+        <v>38742</v>
+      </c>
+      <c r="V139" s="20" t="n">
+        <v>8938</v>
+      </c>
+      <c r="W139" s="20" t="n">
+        <v>9473</v>
+      </c>
+      <c r="X139" s="20" t="n">
+        <v>17147</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M140" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N140" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O140" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P140" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q140" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R140" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S140" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T140" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U140" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V140" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W140" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X140" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y140" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z140" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA140" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB140" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC140" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>해외 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F140" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I140" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="M140" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="20" t="n">
+        <v>1209</v>
+      </c>
+      <c r="W140" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="E141" s="12" t="n">
-        <v>2463</v>
-      </c>
-      <c r="I141" s="12" t="n">
-        <v>7484</v>
-      </c>
-      <c r="M141" s="12" t="n">
-        <v>13322</v>
-      </c>
-      <c r="O141" s="12" t="n">
-        <v>1690</v>
-      </c>
-      <c r="P141" s="12" t="n">
-        <v>2428</v>
-      </c>
-      <c r="Q141" s="12" t="n">
-        <v>2639</v>
-      </c>
-      <c r="R141" s="12" t="n">
-        <v>4374</v>
-      </c>
-      <c r="S141" s="12" t="n">
-        <v>4561</v>
-      </c>
-      <c r="T141" s="12" t="n">
-        <v>8478</v>
-      </c>
-      <c r="U141" s="12" t="n">
-        <v>6589</v>
-      </c>
-      <c r="V141" s="12" t="n">
-        <v>2463</v>
-      </c>
-      <c r="W141" s="12" t="n">
-        <v>7484</v>
-      </c>
-      <c r="X141" s="12" t="n">
-        <v>13322</v>
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="F141" s="20" t="n">
+        <v>14006</v>
+      </c>
+      <c r="J141" s="20" t="n">
+        <v>10849</v>
+      </c>
+      <c r="N141" s="20" t="n">
+        <v>38742</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>일본 · 계</t>
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>223</v>
+        <v>38500</v>
+      </c>
+      <c r="F142" s="20" t="n">
+        <v>44327</v>
       </c>
       <c r="I142" s="20" t="n">
-        <v>231</v>
+        <v>39697</v>
+      </c>
+      <c r="J142" s="20" t="n">
+        <v>38159</v>
       </c>
       <c r="M142" s="20" t="n">
-        <v>265</v>
-      </c>
-      <c r="O142" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="P142" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q142" s="20" t="n">
-        <v>78</v>
-      </c>
-      <c r="R142" s="20" t="n">
-        <v>112</v>
-      </c>
-      <c r="S142" s="20" t="n">
-        <v>113</v>
-      </c>
-      <c r="T142" s="20" t="n">
-        <v>149</v>
-      </c>
-      <c r="U142" s="20" t="n">
-        <v>364</v>
+        <v>68259</v>
+      </c>
+      <c r="N142" s="20" t="n">
+        <v>171337</v>
       </c>
       <c r="V142" s="20" t="n">
-        <v>223</v>
+        <v>38500</v>
       </c>
       <c r="W142" s="20" t="n">
-        <v>231</v>
+        <v>39697</v>
       </c>
       <c r="X142" s="20" t="n">
-        <v>265</v>
+        <v>68259</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="18" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E143" s="20" t="n">
-        <v>65</v>
-      </c>
-      <c r="I143" s="20" t="n">
-        <v>-8</v>
-      </c>
-      <c r="M143" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="O143" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P143" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q143" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" s="20" t="n">
-        <v>59</v>
-      </c>
-      <c r="S143" s="20" t="n">
-        <v>-5</v>
-      </c>
-      <c r="T143" s="20" t="n">
-        <v>147</v>
-      </c>
-      <c r="U143" s="20" t="n">
-        <v>-47</v>
-      </c>
-      <c r="V143" s="20" t="n">
-        <v>65</v>
-      </c>
-      <c r="W143" s="20" t="n">
-        <v>-8</v>
-      </c>
-      <c r="X143" s="20" t="n">
-        <v>37</v>
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I143" s="15">
+        <f>IF(OR(I142="",E142=""),"",IF(E142&lt;=0,"",IFERROR(I142/E142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J143" s="15">
+        <f>IF(OR(J142="",F142=""),"",IF(F142&lt;=0,"",IFERROR(J142/F142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M143" s="15">
+        <f>IF(OR(M142="",I142=""),"",IF(I142&lt;=0,"",IFERROR(M142/I142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N143" s="15">
+        <f>IF(OR(N142="",J142=""),"",IF(J142&lt;=0,"",IFERROR(N142/J142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V143" s="15">
+        <f>IF(OR(V142="",U142=""),"",IF(U142&lt;=0,"",IFERROR(V142/U142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W143" s="15">
+        <f>IF(OR(W142="",V142=""),"",IF(V142&lt;=0,"",IFERROR(W142/V142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X143" s="15">
+        <f>IF(OR(X142="",W142=""),"",IF(W142&lt;=0,"",IFERROR(X142/W142-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>퇴직급여부채 증감</t>
+          <t>해외 · 계</t>
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>55</v>
+        <v>74830</v>
+      </c>
+      <c r="F144" s="20" t="n">
+        <v>72565</v>
       </c>
       <c r="I144" s="20" t="n">
-        <v>27</v>
+        <v>83935</v>
+      </c>
+      <c r="J144" s="20" t="n">
+        <v>75076</v>
       </c>
       <c r="M144" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="O144" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="P144" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q144" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="R144" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="S144" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="T144" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="U144" s="20" t="n">
-        <v>18</v>
+        <v>188210</v>
+      </c>
+      <c r="N144" s="20" t="n">
+        <v>262983</v>
       </c>
       <c r="V144" s="20" t="n">
-        <v>55</v>
+        <v>74830</v>
       </c>
       <c r="W144" s="20" t="n">
-        <v>27</v>
+        <v>83935</v>
       </c>
       <c r="X144" s="20" t="n">
-        <v>-24</v>
+        <v>188210</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="18" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="E145" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="I145" s="20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="M145" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="O145" s="20" t="n">
-        <v>-299</v>
-      </c>
-      <c r="P145" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q145" s="20" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R145" s="20" t="n">
-        <v>-58</v>
-      </c>
-      <c r="S145" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="T145" s="20" t="n">
-        <v>-71</v>
-      </c>
-      <c r="U145" s="20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="V145" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W145" s="20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="X145" s="20" t="n">
-        <v>50</v>
+      <c r="A145" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I145" s="15">
+        <f>IF(OR(I144="",E144=""),"",IF(E144&lt;=0,"",IFERROR(I144/E144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J145" s="15">
+        <f>IF(OR(J144="",F144=""),"",IF(F144&lt;=0,"",IFERROR(J144/F144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M145" s="15">
+        <f>IF(OR(M144="",I144=""),"",IF(I144&lt;=0,"",IFERROR(M144/I144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N145" s="15">
+        <f>IF(OR(N144="",J144=""),"",IF(J144&lt;=0,"",IFERROR(N144/J144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V145" s="15">
+        <f>IF(OR(V144="",U144=""),"",IF(U144&lt;=0,"",IFERROR(V144/U144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W145" s="15">
+        <f>IF(OR(W144="",V144=""),"",IF(V144&lt;=0,"",IFERROR(W144/V144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X145" s="15">
+        <f>IF(OR(X144="",W144=""),"",IF(W144&lt;=0,"",IFERROR(X144/W144-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>지분법손익</t>
-        </is>
-      </c>
-      <c r="E146" s="20" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I146" s="20" t="n">
-        <v>-27</v>
-      </c>
-      <c r="M146" s="20" t="n">
-        <v>-29</v>
-      </c>
-      <c r="O146" s="20" t="n">
-        <v>-40</v>
-      </c>
-      <c r="P146" s="20" t="n">
-        <v>-73</v>
-      </c>
-      <c r="Q146" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="R146" s="20" t="n">
-        <v>-43</v>
-      </c>
-      <c r="S146" s="20" t="n">
-        <v>-15</v>
-      </c>
-      <c r="T146" s="20" t="n">
-        <v>-39</v>
-      </c>
-      <c r="U146" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="V146" s="20" t="n">
-        <v>-22</v>
-      </c>
-      <c r="W146" s="20" t="n">
-        <v>-27</v>
-      </c>
-      <c r="X146" s="20" t="n">
-        <v>-29</v>
+          <t>보고부문 합계 · 계</t>
+        </is>
+      </c>
+      <c r="F146" s="20" t="n">
+        <v>116893</v>
+      </c>
+      <c r="J146" s="20" t="n">
+        <v>113236</v>
+      </c>
+      <c r="N146" s="20" t="n">
+        <v>434321</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="18" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="E147" s="20" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I147" s="20" t="n">
-        <v>-35</v>
-      </c>
-      <c r="M147" s="20" t="n">
-        <v>-37</v>
-      </c>
-      <c r="O147" s="20" t="n">
-        <v>-20</v>
-      </c>
-      <c r="P147" s="20" t="n">
-        <v>-20</v>
-      </c>
-      <c r="Q147" s="20" t="n">
-        <v>-18</v>
-      </c>
-      <c r="R147" s="20" t="n">
-        <v>-198</v>
-      </c>
-      <c r="S147" s="20" t="n">
-        <v>-26</v>
-      </c>
-      <c r="T147" s="20" t="n">
-        <v>-22</v>
-      </c>
-      <c r="U147" s="20" t="n">
-        <v>-21</v>
-      </c>
-      <c r="V147" s="20" t="n">
-        <v>-18</v>
-      </c>
-      <c r="W147" s="20" t="n">
-        <v>-35</v>
-      </c>
-      <c r="X147" s="20" t="n">
-        <v>-37</v>
+      <c r="A147" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="J147" s="15">
+        <f>IF(OR(J146="",F146=""),"",IF(F146&lt;=0,"",IFERROR(J146/F146-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N147" s="15">
+        <f>IF(OR(N146="",J146=""),"",IF(J146&lt;=0,"",IFERROR(N146/J146-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>일본 · 부문 이익</t>
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>1539</v>
+        <v>740</v>
+      </c>
+      <c r="F148" s="20" t="n">
+        <v>2052</v>
       </c>
       <c r="I148" s="20" t="n">
-        <v>1798</v>
+        <v>-159</v>
+      </c>
+      <c r="J148" s="20" t="n">
+        <v>654</v>
       </c>
       <c r="M148" s="20" t="n">
-        <v>2066</v>
-      </c>
-      <c r="O148" s="20" t="n">
-        <v>132</v>
-      </c>
-      <c r="P148" s="20" t="n">
-        <v>214</v>
-      </c>
-      <c r="Q148" s="20" t="n">
-        <v>391</v>
-      </c>
-      <c r="R148" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="S148" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="T148" s="20" t="n">
-        <v>108</v>
-      </c>
-      <c r="U148" s="20" t="n">
-        <v>1199</v>
+        <v>66</v>
+      </c>
+      <c r="N148" s="20" t="n">
+        <v>12782</v>
       </c>
       <c r="V148" s="20" t="n">
-        <v>1539</v>
+        <v>740</v>
       </c>
       <c r="W148" s="20" t="n">
-        <v>1798</v>
+        <v>-159</v>
       </c>
       <c r="X148" s="20" t="n">
-        <v>2066</v>
+        <v>66</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="18" t="inlineStr">
-        <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="E149" s="20" t="n">
-        <v>-178</v>
-      </c>
-      <c r="I149" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="M149" s="20" t="n">
-        <v>-233</v>
-      </c>
-      <c r="O149" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P149" s="20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="Q149" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="R149" s="20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="S149" s="20" t="n">
-        <v>205</v>
-      </c>
-      <c r="T149" s="20" t="n">
-        <v>214</v>
-      </c>
-      <c r="U149" s="20" t="n">
-        <v>-40</v>
-      </c>
-      <c r="V149" s="20" t="n">
-        <v>-178</v>
-      </c>
-      <c r="W149" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="X149" s="20" t="n">
-        <v>-233</v>
+      <c r="A149" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="E149" s="15">
+        <f>IF(OR(E148="",E142=""),"",IF(E142&lt;=0,"",IFERROR(E148/E142,"")))</f>
+        <v/>
+      </c>
+      <c r="F149" s="15">
+        <f>IF(OR(F148="",F142=""),"",IF(F142&lt;=0,"",IFERROR(F148/F142,"")))</f>
+        <v/>
+      </c>
+      <c r="I149" s="15">
+        <f>IF(OR(I148="",I142=""),"",IF(I142&lt;=0,"",IFERROR(I148/I142,"")))</f>
+        <v/>
+      </c>
+      <c r="J149" s="15">
+        <f>IF(OR(J148="",J142=""),"",IF(J142&lt;=0,"",IFERROR(J148/J142,"")))</f>
+        <v/>
+      </c>
+      <c r="M149" s="15">
+        <f>IF(OR(M148="",M142=""),"",IF(M142&lt;=0,"",IFERROR(M148/M142,"")))</f>
+        <v/>
+      </c>
+      <c r="N149" s="15">
+        <f>IF(OR(N148="",N142=""),"",IF(N142&lt;=0,"",IFERROR(N148/N142,"")))</f>
+        <v/>
+      </c>
+      <c r="V149" s="15">
+        <f>IF(OR(V148="",V142=""),"",IF(V142&lt;=0,"",IFERROR(V148/V142,"")))</f>
+        <v/>
+      </c>
+      <c r="W149" s="15">
+        <f>IF(OR(W148="",W142=""),"",IF(W142&lt;=0,"",IFERROR(W148/W142,"")))</f>
+        <v/>
+      </c>
+      <c r="X149" s="15">
+        <f>IF(OR(X148="",X142=""),"",IF(X142&lt;=0,"",IFERROR(X148/X142,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="18" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
-      </c>
-      <c r="E150" s="20" t="n">
-        <v>-445</v>
-      </c>
-      <c r="I150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="20" t="n">
-        <v>-445</v>
-      </c>
-      <c r="W150" s="20" t="n">
-        <v>0</v>
+      <c r="A150" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I150" s="15">
+        <f>IF(OR(I148="",E148=""),"",IF(E148&lt;=0,"",IFERROR(I148/E148-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J150" s="15">
+        <f>IF(OR(J148="",F148=""),"",IF(F148&lt;=0,"",IFERROR(J148/F148-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M150" s="15">
+        <f>IF(OR(M148="",I148=""),"",IF(I148&lt;=0,"",IFERROR(M148/I148-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N150" s="15">
+        <f>IF(OR(N148="",J148=""),"",IF(J148&lt;=0,"",IFERROR(N148/J148-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V150" s="15">
+        <f>IF(OR(V148="",U148=""),"",IF(U148&lt;=0,"",IFERROR(V148/U148-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W150" s="15">
+        <f>IF(OR(W148="",V148=""),"",IF(V148&lt;=0,"",IFERROR(W148/V148-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X150" s="15">
+        <f>IF(OR(X148="",W148=""),"",IF(W148&lt;=0,"",IFERROR(X148/W148-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>해외 · 부문 이익</t>
         </is>
       </c>
       <c r="E151" s="20" t="n">
-        <v>-4426</v>
+        <v>1510</v>
+      </c>
+      <c r="F151" s="20" t="n">
+        <v>1185</v>
       </c>
       <c r="I151" s="20" t="n">
-        <v>5151</v>
+        <v>1687</v>
+      </c>
+      <c r="J151" s="20" t="n">
+        <v>1252</v>
       </c>
       <c r="M151" s="20" t="n">
-        <v>-43312</v>
-      </c>
-      <c r="O151" s="20" t="n">
-        <v>2008</v>
-      </c>
-      <c r="P151" s="20" t="n">
-        <v>-11172</v>
-      </c>
-      <c r="Q151" s="20" t="n">
-        <v>-4004</v>
-      </c>
-      <c r="R151" s="20" t="n">
-        <v>-7028</v>
-      </c>
-      <c r="S151" s="20" t="n">
-        <v>-6982</v>
-      </c>
-      <c r="T151" s="20" t="n">
-        <v>-1264</v>
-      </c>
-      <c r="U151" s="20" t="n">
-        <v>13575</v>
+        <v>5129</v>
+      </c>
+      <c r="N151" s="20" t="n">
+        <v>9583</v>
       </c>
       <c r="V151" s="20" t="n">
-        <v>-4426</v>
+        <v>1510</v>
       </c>
       <c r="W151" s="20" t="n">
-        <v>5151</v>
+        <v>1687</v>
       </c>
       <c r="X151" s="20" t="n">
-        <v>-43312</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="18" t="inlineStr">
-        <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="E152" s="20" t="n">
-        <v>-3423</v>
-      </c>
-      <c r="I152" s="20" t="n">
-        <v>1140</v>
-      </c>
-      <c r="M152" s="20" t="n">
-        <v>-170870</v>
-      </c>
-      <c r="O152" s="20" t="n">
-        <v>-178</v>
-      </c>
-      <c r="P152" s="20" t="n">
-        <v>-455</v>
-      </c>
-      <c r="Q152" s="20" t="n">
-        <v>88</v>
-      </c>
-      <c r="R152" s="20" t="n">
-        <v>-11127</v>
-      </c>
-      <c r="S152" s="20" t="n">
-        <v>-20492</v>
-      </c>
-      <c r="T152" s="20" t="n">
-        <v>5740</v>
-      </c>
-      <c r="U152" s="20" t="n">
-        <v>6224</v>
-      </c>
-      <c r="V152" s="20" t="n">
-        <v>-3423</v>
-      </c>
-      <c r="W152" s="20" t="n">
-        <v>1140</v>
-      </c>
-      <c r="X152" s="20" t="n">
-        <v>-170870</v>
+      <c r="A152" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="E152" s="15">
+        <f>IF(OR(E151="",E144=""),"",IF(E144&lt;=0,"",IFERROR(E151/E144,"")))</f>
+        <v/>
+      </c>
+      <c r="F152" s="15">
+        <f>IF(OR(F151="",F144=""),"",IF(F144&lt;=0,"",IFERROR(F151/F144,"")))</f>
+        <v/>
+      </c>
+      <c r="I152" s="15">
+        <f>IF(OR(I151="",I144=""),"",IF(I144&lt;=0,"",IFERROR(I151/I144,"")))</f>
+        <v/>
+      </c>
+      <c r="J152" s="15">
+        <f>IF(OR(J151="",J144=""),"",IF(J144&lt;=0,"",IFERROR(J151/J144,"")))</f>
+        <v/>
+      </c>
+      <c r="M152" s="15">
+        <f>IF(OR(M151="",M144=""),"",IF(M144&lt;=0,"",IFERROR(M151/M144,"")))</f>
+        <v/>
+      </c>
+      <c r="N152" s="15">
+        <f>IF(OR(N151="",N144=""),"",IF(N144&lt;=0,"",IFERROR(N151/N144,"")))</f>
+        <v/>
+      </c>
+      <c r="V152" s="15">
+        <f>IF(OR(V151="",V144=""),"",IF(V144&lt;=0,"",IFERROR(V151/V144,"")))</f>
+        <v/>
+      </c>
+      <c r="W152" s="15">
+        <f>IF(OR(W151="",W144=""),"",IF(W144&lt;=0,"",IFERROR(W151/W144,"")))</f>
+        <v/>
+      </c>
+      <c r="X152" s="15">
+        <f>IF(OR(X151="",X144=""),"",IF(X144&lt;=0,"",IFERROR(X151/X144,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="18" t="inlineStr">
-        <is>
-          <t>선급금 증감</t>
-        </is>
-      </c>
-      <c r="E153" s="20" t="n">
-        <v>2139</v>
-      </c>
-      <c r="I153" s="20" t="n">
-        <v>109</v>
-      </c>
-      <c r="M153" s="20" t="n">
-        <v>-1379</v>
-      </c>
-      <c r="O153" s="20" t="n">
-        <v>-3188</v>
-      </c>
-      <c r="P153" s="20" t="n">
-        <v>4922</v>
-      </c>
-      <c r="Q153" s="20" t="n">
-        <v>-9494</v>
-      </c>
-      <c r="R153" s="20" t="n">
-        <v>8373</v>
-      </c>
-      <c r="S153" s="20" t="n">
-        <v>1438</v>
-      </c>
-      <c r="T153" s="20" t="n">
-        <v>1387</v>
-      </c>
-      <c r="U153" s="20" t="n">
-        <v>-2444</v>
-      </c>
-      <c r="V153" s="20" t="n">
-        <v>2139</v>
-      </c>
-      <c r="W153" s="20" t="n">
-        <v>109</v>
-      </c>
-      <c r="X153" s="20" t="n">
-        <v>-1379</v>
+      <c r="A153" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="I153" s="15">
+        <f>IF(OR(I151="",E151=""),"",IF(E151&lt;=0,"",IFERROR(I151/E151-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J153" s="15">
+        <f>IF(OR(J151="",F151=""),"",IF(F151&lt;=0,"",IFERROR(J151/F151-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M153" s="15">
+        <f>IF(OR(M151="",I151=""),"",IF(I151&lt;=0,"",IFERROR(M151/I151-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N153" s="15">
+        <f>IF(OR(N151="",J151=""),"",IF(J151&lt;=0,"",IFERROR(N151/J151-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V153" s="15">
+        <f>IF(OR(V151="",U151=""),"",IF(U151&lt;=0,"",IFERROR(V151/U151-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W153" s="15">
+        <f>IF(OR(W151="",V151=""),"",IF(V151&lt;=0,"",IFERROR(W151/V151-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X153" s="15">
+        <f>IF(OR(X151="",W151=""),"",IF(W151&lt;=0,"",IFERROR(X151/W151-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="E154" s="20" t="n">
-        <v>6948</v>
-      </c>
-      <c r="I154" s="20" t="n">
-        <v>-6132</v>
-      </c>
-      <c r="M154" s="20" t="n">
-        <v>63535</v>
-      </c>
-      <c r="O154" s="20" t="n">
-        <v>-3531</v>
-      </c>
-      <c r="P154" s="20" t="n">
-        <v>13254</v>
-      </c>
-      <c r="Q154" s="20" t="n">
-        <v>3421</v>
-      </c>
-      <c r="R154" s="20" t="n">
-        <v>8140</v>
-      </c>
-      <c r="S154" s="20" t="n">
-        <v>8359</v>
-      </c>
-      <c r="T154" s="20" t="n">
-        <v>-418</v>
-      </c>
-      <c r="U154" s="20" t="n">
-        <v>-12740</v>
-      </c>
-      <c r="V154" s="20" t="n">
-        <v>6948</v>
-      </c>
-      <c r="W154" s="20" t="n">
-        <v>-6132</v>
-      </c>
-      <c r="X154" s="20" t="n">
-        <v>63535</v>
+          <t>보고부문 합계 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="F154" s="20" t="n">
+        <v>3237</v>
+      </c>
+      <c r="J154" s="20" t="n">
+        <v>1907</v>
+      </c>
+      <c r="N154" s="20" t="n">
+        <v>22366</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="18" t="inlineStr">
-        <is>
-          <t>선수금 증감</t>
-        </is>
-      </c>
-      <c r="E155" s="20" t="n">
-        <v>840</v>
-      </c>
-      <c r="I155" s="20" t="n">
-        <v>407</v>
-      </c>
-      <c r="M155" s="20" t="n">
-        <v>45699</v>
-      </c>
-      <c r="P155" s="20" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q155" s="20" t="n">
-        <v>2811</v>
-      </c>
-      <c r="R155" s="20" t="n">
-        <v>6177</v>
-      </c>
-      <c r="S155" s="20" t="n">
-        <v>967</v>
-      </c>
-      <c r="T155" s="20" t="n">
-        <v>-10187</v>
-      </c>
-      <c r="U155" s="20" t="n">
-        <v>-272</v>
-      </c>
-      <c r="V155" s="20" t="n">
-        <v>840</v>
-      </c>
-      <c r="W155" s="20" t="n">
-        <v>407</v>
-      </c>
-      <c r="X155" s="20" t="n">
-        <v>45699</v>
+      <c r="A155" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="F155" s="15">
+        <f>IF(OR(F154="",F146=""),"",IF(F146&lt;=0,"",IFERROR(F154/F146,"")))</f>
+        <v/>
+      </c>
+      <c r="J155" s="15">
+        <f>IF(OR(J154="",J146=""),"",IF(J146&lt;=0,"",IFERROR(J154/J146,"")))</f>
+        <v/>
+      </c>
+      <c r="N155" s="15">
+        <f>IF(OR(N154="",N146=""),"",IF(N146&lt;=0,"",IFERROR(N154/N146,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="18" t="inlineStr">
-        <is>
-          <t>미지급금 증감</t>
-        </is>
-      </c>
-      <c r="E156" s="20" t="n">
-        <v>2033</v>
-      </c>
-      <c r="I156" s="20" t="n">
-        <v>1035</v>
-      </c>
-      <c r="M156" s="20" t="n">
-        <v>-2607</v>
-      </c>
-      <c r="O156" s="20" t="n">
-        <v>12814</v>
-      </c>
-      <c r="P156" s="20" t="n">
-        <v>-10668</v>
-      </c>
-      <c r="Q156" s="20" t="n">
-        <v>4040</v>
-      </c>
-      <c r="R156" s="20" t="n">
-        <v>1610</v>
-      </c>
-      <c r="S156" s="20" t="n">
-        <v>2470</v>
-      </c>
-      <c r="T156" s="20" t="n">
-        <v>373</v>
-      </c>
-      <c r="U156" s="20" t="n">
-        <v>-12687</v>
-      </c>
-      <c r="V156" s="20" t="n">
-        <v>2033</v>
-      </c>
-      <c r="W156" s="20" t="n">
-        <v>1035</v>
-      </c>
-      <c r="X156" s="20" t="n">
-        <v>-2607</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="18" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E157" s="20" t="n">
-        <v>-587</v>
-      </c>
-      <c r="I157" s="20" t="n">
-        <v>-183</v>
-      </c>
-      <c r="M157" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="O157" s="20" t="n">
-        <v>961</v>
-      </c>
-      <c r="P157" s="20" t="n">
-        <v>-488</v>
-      </c>
-      <c r="Q157" s="20" t="n">
-        <v>549</v>
-      </c>
-      <c r="R157" s="20" t="n">
-        <v>-322</v>
-      </c>
-      <c r="S157" s="20" t="n">
-        <v>-1106</v>
-      </c>
-      <c r="T157" s="20" t="n">
-        <v>2552</v>
-      </c>
-      <c r="U157" s="20" t="n">
-        <v>-1030</v>
-      </c>
-      <c r="V157" s="20" t="n">
-        <v>-587</v>
-      </c>
-      <c r="W157" s="20" t="n">
-        <v>-183</v>
-      </c>
-      <c r="X157" s="20" t="n">
-        <v>38</v>
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="J156" s="15">
+        <f>IF(OR(J154="",F154=""),"",IF(F154&lt;=0,"",IFERROR(J154/F154-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N156" s="15">
+        <f>IF(OR(N154="",J154=""),"",IF(J154&lt;=0,"",IFERROR(N154/J154-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="18" t="inlineStr">
-        <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="E158" s="20" t="n">
-        <v>7216</v>
-      </c>
-      <c r="I158" s="20" t="n">
-        <v>11042</v>
-      </c>
-      <c r="M158" s="20" t="n">
-        <v>-93480</v>
-      </c>
-      <c r="O158" s="20" t="n">
-        <v>10407</v>
-      </c>
-      <c r="P158" s="20" t="n">
-        <v>-1740</v>
-      </c>
-      <c r="Q158" s="20" t="n">
-        <v>561</v>
-      </c>
-      <c r="R158" s="20" t="n">
-        <v>10158</v>
-      </c>
-      <c r="S158" s="20" t="n">
-        <v>-10422</v>
-      </c>
-      <c r="T158" s="20" t="n">
-        <v>7167</v>
-      </c>
-      <c r="U158" s="20" t="n">
-        <v>-1311</v>
-      </c>
-      <c r="V158" s="20" t="n">
-        <v>7216</v>
-      </c>
-      <c r="W158" s="20" t="n">
-        <v>11042</v>
-      </c>
-      <c r="X158" s="20" t="n">
-        <v>-93480</v>
-      </c>
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B158" s="42" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="n"/>
+      <c r="D158" s="16" t="n"/>
+      <c r="E158" s="16" t="n"/>
+      <c r="F158" s="16" t="n"/>
+      <c r="G158" s="16" t="n"/>
+      <c r="H158" s="16" t="n"/>
+      <c r="I158" s="16" t="n"/>
+      <c r="J158" s="16" t="n"/>
+      <c r="K158" s="16" t="n"/>
+      <c r="L158" s="16" t="n"/>
+      <c r="M158" s="16" t="n"/>
+      <c r="N158" s="16" t="n"/>
+      <c r="O158" s="16" t="n"/>
+      <c r="P158" s="16" t="n"/>
+      <c r="Q158" s="16" t="n"/>
+      <c r="R158" s="16" t="n"/>
+      <c r="S158" s="16" t="n"/>
+      <c r="T158" s="16" t="n"/>
+      <c r="U158" s="16" t="n"/>
+      <c r="V158" s="16" t="n"/>
+      <c r="W158" s="16" t="n"/>
+      <c r="X158" s="16" t="n"/>
+      <c r="Y158" s="16" t="n"/>
+      <c r="Z158" s="16" t="n"/>
+      <c r="AA158" s="16" t="n"/>
+      <c r="AB158" s="16" t="n"/>
+      <c r="AC158" s="16" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="18" t="inlineStr">
-        <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="E159" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="I159" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="M159" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="O159" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="P159" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q159" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="R159" s="20" t="n">
-        <v>209</v>
-      </c>
-      <c r="S159" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="T159" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="U159" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="V159" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="W159" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="X159" s="20" t="n">
-        <v>41</v>
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P159" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q159" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S159" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T159" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U159" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V159" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W159" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X159" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y159" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z159" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA159" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB159" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC159" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="18" t="inlineStr">
-        <is>
-          <t>이자 지급</t>
-        </is>
-      </c>
-      <c r="E160" s="20" t="n">
-        <v>-1539</v>
-      </c>
-      <c r="I160" s="20" t="n">
-        <v>-1798</v>
-      </c>
-      <c r="M160" s="20" t="n">
-        <v>-2066</v>
-      </c>
-      <c r="O160" s="20" t="n">
-        <v>-132</v>
-      </c>
-      <c r="P160" s="20" t="n">
-        <v>-214</v>
-      </c>
-      <c r="Q160" s="20" t="n">
-        <v>-391</v>
-      </c>
-      <c r="R160" s="20" t="n">
-        <v>-55</v>
-      </c>
-      <c r="S160" s="20" t="n">
-        <v>-17</v>
-      </c>
-      <c r="T160" s="20" t="n">
-        <v>-108</v>
-      </c>
-      <c r="U160" s="20" t="n">
-        <v>-1199</v>
-      </c>
-      <c r="V160" s="20" t="n">
-        <v>-1539</v>
-      </c>
-      <c r="W160" s="20" t="n">
-        <v>-1798</v>
-      </c>
-      <c r="X160" s="20" t="n">
-        <v>-2066</v>
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="n">
+        <v>2463</v>
+      </c>
+      <c r="I160" s="12" t="n">
+        <v>7484</v>
+      </c>
+      <c r="M160" s="12" t="n">
+        <v>13322</v>
+      </c>
+      <c r="O160" s="12" t="n">
+        <v>1690</v>
+      </c>
+      <c r="P160" s="12" t="n">
+        <v>2428</v>
+      </c>
+      <c r="Q160" s="12" t="n">
+        <v>2639</v>
+      </c>
+      <c r="R160" s="12" t="n">
+        <v>4374</v>
+      </c>
+      <c r="S160" s="12" t="n">
+        <v>4561</v>
+      </c>
+      <c r="T160" s="12" t="n">
+        <v>8478</v>
+      </c>
+      <c r="U160" s="12" t="n">
+        <v>6589</v>
+      </c>
+      <c r="V160" s="12" t="n">
+        <v>2463</v>
+      </c>
+      <c r="W160" s="12" t="n">
+        <v>7484</v>
+      </c>
+      <c r="X160" s="12" t="n">
+        <v>13322</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E161" s="20" t="n">
-        <v>-1270</v>
+        <v>223</v>
       </c>
       <c r="I161" s="20" t="n">
-        <v>-604</v>
+        <v>231</v>
       </c>
       <c r="M161" s="20" t="n">
-        <v>-1962</v>
+        <v>265</v>
       </c>
       <c r="O161" s="20" t="n">
-        <v>-709</v>
+        <v>18</v>
       </c>
       <c r="P161" s="20" t="n">
-        <v>-295</v>
+        <v>22</v>
       </c>
       <c r="Q161" s="20" t="n">
-        <v>-769</v>
+        <v>78</v>
       </c>
       <c r="R161" s="20" t="n">
-        <v>-758</v>
+        <v>112</v>
       </c>
       <c r="S161" s="20" t="n">
-        <v>-1177</v>
+        <v>113</v>
       </c>
       <c r="T161" s="20" t="n">
-        <v>-1192</v>
+        <v>149</v>
       </c>
       <c r="U161" s="20" t="n">
-        <v>-2479</v>
+        <v>364</v>
       </c>
       <c r="V161" s="20" t="n">
-        <v>-1270</v>
+        <v>223</v>
       </c>
       <c r="W161" s="20" t="n">
-        <v>-604</v>
+        <v>231</v>
       </c>
       <c r="X161" s="20" t="n">
-        <v>-1962</v>
+        <v>265</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E162" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I162" s="20" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M162" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="O162" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P162" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q162" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I162" s="20" t="n">
-        <v>525</v>
-      </c>
-      <c r="M162" s="20" t="n">
-        <v>0</v>
+      <c r="R162" s="20" t="n">
+        <v>59</v>
+      </c>
+      <c r="S162" s="20" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T162" s="20" t="n">
+        <v>147</v>
+      </c>
+      <c r="U162" s="20" t="n">
+        <v>-47</v>
       </c>
       <c r="V162" s="20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="W162" s="20" t="n">
-        <v>525</v>
+        <v>-8</v>
       </c>
       <c r="X162" s="20" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E163" s="12" t="n">
-        <v>4425</v>
-      </c>
-      <c r="I163" s="12" t="n">
-        <v>9210</v>
-      </c>
-      <c r="M163" s="12" t="n">
-        <v>-97467</v>
-      </c>
-      <c r="O163" s="12" t="n">
-        <v>9586</v>
-      </c>
-      <c r="P163" s="12" t="n">
-        <v>-2229</v>
-      </c>
-      <c r="Q163" s="12" t="n">
-        <v>-570</v>
-      </c>
-      <c r="R163" s="12" t="n">
-        <v>9554</v>
-      </c>
-      <c r="S163" s="12" t="n">
-        <v>-11583</v>
-      </c>
-      <c r="T163" s="12" t="n">
-        <v>5896</v>
-      </c>
-      <c r="U163" s="12" t="n">
-        <v>-4961</v>
-      </c>
-      <c r="V163" s="12" t="n">
-        <v>4425</v>
-      </c>
-      <c r="W163" s="12" t="n">
-        <v>9210</v>
-      </c>
-      <c r="X163" s="12" t="n">
-        <v>-97467</v>
+      <c r="A163" s="18" t="inlineStr">
+        <is>
+          <t>퇴직급여부채 증감</t>
+        </is>
+      </c>
+      <c r="E163" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I163" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="M163" s="20" t="n">
+        <v>-24</v>
+      </c>
+      <c r="O163" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="P163" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q163" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="R163" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="S163" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="T163" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="U163" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="V163" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="W163" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="X163" s="20" t="n">
+        <v>-24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>-17</v>
+        <v>8</v>
       </c>
       <c r="I164" s="20" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M164" s="20" t="n">
-        <v>-88</v>
+        <v>50</v>
       </c>
       <c r="O164" s="20" t="n">
-        <v>-10</v>
+        <v>-299</v>
       </c>
       <c r="P164" s="20" t="n">
-        <v>-11</v>
+        <v>17</v>
       </c>
       <c r="Q164" s="20" t="n">
         <v>-5</v>
       </c>
       <c r="R164" s="20" t="n">
-        <v>-8</v>
+        <v>-58</v>
       </c>
       <c r="S164" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T164" s="20" t="n">
+        <v>-71</v>
+      </c>
+      <c r="U164" s="20" t="n">
         <v>-7</v>
       </c>
-      <c r="T164" s="20" t="n">
-        <v>-149</v>
-      </c>
-      <c r="U164" s="20" t="n">
-        <v>-206</v>
-      </c>
       <c r="V164" s="20" t="n">
-        <v>-17</v>
+        <v>8</v>
       </c>
       <c r="W164" s="20" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="X164" s="20" t="n">
-        <v>-88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>지분법손익</t>
         </is>
       </c>
       <c r="E165" s="20" t="n">
-        <v>-258</v>
+        <v>-22</v>
       </c>
       <c r="I165" s="20" t="n">
-        <v>-23</v>
+        <v>-27</v>
       </c>
       <c r="M165" s="20" t="n">
-        <v>-26</v>
+        <v>-29</v>
       </c>
       <c r="O165" s="20" t="n">
+        <v>-40</v>
+      </c>
+      <c r="P165" s="20" t="n">
+        <v>-73</v>
+      </c>
+      <c r="Q165" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="R165" s="20" t="n">
+        <v>-43</v>
+      </c>
+      <c r="S165" s="20" t="n">
+        <v>-15</v>
+      </c>
+      <c r="T165" s="20" t="n">
+        <v>-39</v>
+      </c>
+      <c r="U165" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="V165" s="20" t="n">
+        <v>-22</v>
+      </c>
+      <c r="W165" s="20" t="n">
+        <v>-27</v>
+      </c>
+      <c r="X165" s="20" t="n">
         <v>-29</v>
-      </c>
-      <c r="P165" s="20" t="n">
-        <v>-47</v>
-      </c>
-      <c r="Q165" s="20" t="n">
-        <v>-234</v>
-      </c>
-      <c r="R165" s="20" t="n">
-        <v>-8</v>
-      </c>
-      <c r="S165" s="20" t="n">
-        <v>-19</v>
-      </c>
-      <c r="T165" s="20" t="n">
-        <v>-6</v>
-      </c>
-      <c r="U165" s="20" t="n">
-        <v>-82</v>
-      </c>
-      <c r="V165" s="20" t="n">
-        <v>-258</v>
-      </c>
-      <c r="W165" s="20" t="n">
-        <v>-23</v>
-      </c>
-      <c r="X165" s="20" t="n">
-        <v>-26</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>741</v>
+        <v>-18</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>0</v>
+        <v>-35</v>
+      </c>
+      <c r="M166" s="20" t="n">
+        <v>-37</v>
+      </c>
+      <c r="O166" s="20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="P166" s="20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Q166" s="20" t="n">
+        <v>-18</v>
+      </c>
+      <c r="R166" s="20" t="n">
+        <v>-198</v>
+      </c>
+      <c r="S166" s="20" t="n">
+        <v>-26</v>
+      </c>
+      <c r="T166" s="20" t="n">
+        <v>-22</v>
       </c>
       <c r="U166" s="20" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="V166" s="20" t="n">
-        <v>741</v>
+        <v>-18</v>
       </c>
       <c r="W166" s="20" t="n">
-        <v>0</v>
+        <v>-35</v>
+      </c>
+      <c r="X166" s="20" t="n">
+        <v>-37</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E167" s="20" t="n">
-        <v>28</v>
+        <v>1539</v>
       </c>
       <c r="I167" s="20" t="n">
-        <v>8</v>
+        <v>1798</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>-248</v>
+        <v>2066</v>
       </c>
       <c r="O167" s="20" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="P167" s="20" t="n">
-        <v>-3</v>
+        <v>214</v>
       </c>
       <c r="Q167" s="20" t="n">
-        <v>9</v>
+        <v>391</v>
       </c>
       <c r="R167" s="20" t="n">
-        <v>-1</v>
+        <v>55</v>
       </c>
       <c r="S167" s="20" t="n">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="T167" s="20" t="n">
-        <v>-27</v>
+        <v>108</v>
       </c>
       <c r="U167" s="20" t="n">
-        <v>25</v>
+        <v>1199</v>
       </c>
       <c r="V167" s="20" t="n">
-        <v>28</v>
+        <v>1539</v>
       </c>
       <c r="W167" s="20" t="n">
-        <v>8</v>
+        <v>1798</v>
       </c>
       <c r="X167" s="20" t="n">
-        <v>-248</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E168" s="12" t="n">
-        <v>494</v>
-      </c>
-      <c r="I168" s="12" t="n">
-        <v>-21</v>
-      </c>
-      <c r="M168" s="12" t="n">
-        <v>-362</v>
-      </c>
-      <c r="O168" s="12" t="n">
-        <v>-37</v>
-      </c>
-      <c r="P168" s="12" t="n">
-        <v>-62</v>
-      </c>
-      <c r="Q168" s="12" t="n">
-        <v>-229</v>
-      </c>
-      <c r="R168" s="12" t="n">
-        <v>-17</v>
-      </c>
-      <c r="S168" s="12" t="n">
-        <v>-30</v>
-      </c>
-      <c r="T168" s="12" t="n">
-        <v>-183</v>
-      </c>
-      <c r="U168" s="12" t="n">
-        <v>-263</v>
-      </c>
-      <c r="V168" s="12" t="n">
-        <v>494</v>
-      </c>
-      <c r="W168" s="12" t="n">
-        <v>-21</v>
-      </c>
-      <c r="X168" s="12" t="n">
-        <v>-362</v>
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>외환차손익</t>
+        </is>
+      </c>
+      <c r="E168" s="20" t="n">
+        <v>-178</v>
+      </c>
+      <c r="I168" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="M168" s="20" t="n">
+        <v>-233</v>
+      </c>
+      <c r="O168" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P168" s="20" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Q168" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R168" s="20" t="n">
+        <v>-7</v>
+      </c>
+      <c r="S168" s="20" t="n">
+        <v>205</v>
+      </c>
+      <c r="T168" s="20" t="n">
+        <v>214</v>
+      </c>
+      <c r="U168" s="20" t="n">
+        <v>-40</v>
+      </c>
+      <c r="V168" s="20" t="n">
+        <v>-178</v>
+      </c>
+      <c r="W168" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="X168" s="20" t="n">
+        <v>-233</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>투자유가증권 매각손익</t>
         </is>
       </c>
       <c r="E169" s="20" t="n">
-        <v>6059</v>
+        <v>-445</v>
       </c>
       <c r="I169" s="20" t="n">
-        <v>-15547</v>
-      </c>
-      <c r="M169" s="20" t="n">
-        <v>98097</v>
-      </c>
-      <c r="O169" s="20" t="n">
-        <v>3364</v>
-      </c>
-      <c r="P169" s="20" t="n">
-        <v>-6554</v>
-      </c>
-      <c r="Q169" s="20" t="n">
-        <v>-511</v>
-      </c>
-      <c r="R169" s="20" t="n">
-        <v>-5648</v>
-      </c>
-      <c r="S169" s="20" t="n">
-        <v>13889</v>
-      </c>
-      <c r="T169" s="20" t="n">
-        <v>-5941</v>
+        <v>0</v>
       </c>
       <c r="U169" s="20" t="n">
-        <v>10669</v>
+        <v>0</v>
       </c>
       <c r="V169" s="20" t="n">
-        <v>6059</v>
+        <v>-445</v>
       </c>
       <c r="W169" s="20" t="n">
-        <v>-15547</v>
-      </c>
-      <c r="X169" s="20" t="n">
-        <v>98097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>-91</v>
+        <v>-4426</v>
       </c>
       <c r="I170" s="20" t="n">
-        <v>54</v>
+        <v>5151</v>
+      </c>
+      <c r="M170" s="20" t="n">
+        <v>-43312</v>
+      </c>
+      <c r="O170" s="20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="P170" s="20" t="n">
+        <v>-11172</v>
       </c>
       <c r="Q170" s="20" t="n">
-        <v>0</v>
+        <v>-4004</v>
       </c>
       <c r="R170" s="20" t="n">
-        <v>-36</v>
+        <v>-7028</v>
       </c>
       <c r="S170" s="20" t="n">
-        <v>-37</v>
+        <v>-6982</v>
       </c>
       <c r="T170" s="20" t="n">
-        <v>-24</v>
+        <v>-1264</v>
       </c>
       <c r="U170" s="20" t="n">
-        <v>-43</v>
+        <v>13575</v>
       </c>
       <c r="V170" s="20" t="n">
-        <v>-91</v>
+        <v>-4426</v>
       </c>
       <c r="W170" s="20" t="n">
-        <v>54</v>
+        <v>5151</v>
+      </c>
+      <c r="X170" s="20" t="n">
+        <v>-43312</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="E171" s="20" t="n">
-        <v>-0</v>
+        <v>-3423</v>
       </c>
       <c r="I171" s="20" t="n">
-        <v>-0</v>
+        <v>1140</v>
+      </c>
+      <c r="M171" s="20" t="n">
+        <v>-170870</v>
       </c>
       <c r="O171" s="20" t="n">
-        <v>-0</v>
+        <v>-178</v>
       </c>
       <c r="P171" s="20" t="n">
-        <v>-0</v>
+        <v>-455</v>
       </c>
       <c r="Q171" s="20" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R171" s="20" t="n">
-        <v>-0</v>
+        <v>-11127</v>
       </c>
       <c r="S171" s="20" t="n">
-        <v>-0</v>
+        <v>-20492</v>
       </c>
       <c r="T171" s="20" t="n">
-        <v>-0</v>
+        <v>5740</v>
       </c>
       <c r="U171" s="20" t="n">
-        <v>-0</v>
+        <v>6224</v>
       </c>
       <c r="V171" s="20" t="n">
-        <v>-0</v>
+        <v>-3423</v>
       </c>
       <c r="W171" s="20" t="n">
-        <v>-0</v>
+        <v>1140</v>
+      </c>
+      <c r="X171" s="20" t="n">
+        <v>-170870</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>선급금 증감</t>
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>-2041</v>
+        <v>2139</v>
       </c>
       <c r="I172" s="20" t="n">
-        <v>-1360</v>
+        <v>109</v>
       </c>
       <c r="M172" s="20" t="n">
-        <v>-2040</v>
+        <v>-1379</v>
       </c>
       <c r="O172" s="20" t="n">
-        <v>-339</v>
+        <v>-3188</v>
       </c>
       <c r="P172" s="20" t="n">
-        <v>-408</v>
+        <v>4922</v>
       </c>
       <c r="Q172" s="20" t="n">
-        <v>-544</v>
+        <v>-9494</v>
       </c>
       <c r="R172" s="20" t="n">
-        <v>-612</v>
+        <v>8373</v>
       </c>
       <c r="S172" s="20" t="n">
-        <v>-1020</v>
+        <v>1438</v>
       </c>
       <c r="T172" s="20" t="n">
-        <v>-1156</v>
+        <v>1387</v>
       </c>
       <c r="U172" s="20" t="n">
-        <v>-2040</v>
+        <v>-2444</v>
       </c>
       <c r="V172" s="20" t="n">
-        <v>-2041</v>
+        <v>2139</v>
       </c>
       <c r="W172" s="20" t="n">
-        <v>-1360</v>
+        <v>109</v>
       </c>
       <c r="X172" s="20" t="n">
-        <v>-2040</v>
+        <v>-1379</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>연결범위 변경 없는 자회사 주식 취득</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="E173" s="20" t="n">
-        <v>-1021</v>
+        <v>6948</v>
       </c>
       <c r="I173" s="20" t="n">
-        <v>0</v>
+        <v>-6132</v>
+      </c>
+      <c r="M173" s="20" t="n">
+        <v>63535</v>
+      </c>
+      <c r="O173" s="20" t="n">
+        <v>-3531</v>
+      </c>
+      <c r="P173" s="20" t="n">
+        <v>13254</v>
+      </c>
+      <c r="Q173" s="20" t="n">
+        <v>3421</v>
       </c>
       <c r="R173" s="20" t="n">
-        <v>0</v>
+        <v>8140</v>
       </c>
       <c r="S173" s="20" t="n">
-        <v>-1965</v>
+        <v>8359</v>
       </c>
       <c r="T173" s="20" t="n">
-        <v>-472</v>
+        <v>-418</v>
       </c>
       <c r="U173" s="20" t="n">
-        <v>0</v>
+        <v>-12740</v>
       </c>
       <c r="V173" s="20" t="n">
-        <v>-1021</v>
+        <v>6948</v>
       </c>
       <c r="W173" s="20" t="n">
-        <v>0</v>
+        <v>-6132</v>
+      </c>
+      <c r="X173" s="20" t="n">
+        <v>63535</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>비지배주주 납입</t>
-        </is>
+          <t>선수금 증감</t>
+        </is>
+      </c>
+      <c r="E174" s="20" t="n">
+        <v>840</v>
+      </c>
+      <c r="I174" s="20" t="n">
+        <v>407</v>
+      </c>
+      <c r="M174" s="20" t="n">
+        <v>45699</v>
+      </c>
+      <c r="P174" s="20" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q174" s="20" t="n">
+        <v>2811</v>
       </c>
       <c r="R174" s="20" t="n">
-        <v>0</v>
+        <v>6177</v>
       </c>
       <c r="S174" s="20" t="n">
-        <v>431</v>
+        <v>967</v>
       </c>
       <c r="T174" s="20" t="n">
-        <v>0</v>
+        <v>-10187</v>
+      </c>
+      <c r="U174" s="20" t="n">
+        <v>-272</v>
+      </c>
+      <c r="V174" s="20" t="n">
+        <v>840</v>
+      </c>
+      <c r="W174" s="20" t="n">
+        <v>407</v>
+      </c>
+      <c r="X174" s="20" t="n">
+        <v>45699</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
+          <t>미지급금 증감</t>
+        </is>
+      </c>
+      <c r="E175" s="20" t="n">
+        <v>2033</v>
+      </c>
+      <c r="I175" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="M175" s="20" t="n">
+        <v>-2607</v>
+      </c>
+      <c r="O175" s="20" t="n">
+        <v>12814</v>
+      </c>
+      <c r="P175" s="20" t="n">
+        <v>-10668</v>
+      </c>
+      <c r="Q175" s="20" t="n">
+        <v>4040</v>
+      </c>
+      <c r="R175" s="20" t="n">
+        <v>1610</v>
+      </c>
+      <c r="S175" s="20" t="n">
+        <v>2470</v>
+      </c>
+      <c r="T175" s="20" t="n">
+        <v>373</v>
+      </c>
+      <c r="U175" s="20" t="n">
+        <v>-12687</v>
+      </c>
+      <c r="V175" s="20" t="n">
+        <v>2033</v>
+      </c>
+      <c r="W175" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="X175" s="20" t="n">
+        <v>-2607</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="18" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="I175" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="M175" s="20" t="n">
-        <v>-90</v>
-      </c>
-      <c r="W175" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="X175" s="20" t="n">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E176" s="12" t="n">
-        <v>2904</v>
-      </c>
-      <c r="I176" s="12" t="n">
-        <v>-16853</v>
-      </c>
-      <c r="M176" s="12" t="n">
-        <v>95965</v>
-      </c>
-      <c r="O176" s="12" t="n">
-        <v>3024</v>
-      </c>
-      <c r="P176" s="12" t="n">
-        <v>-6963</v>
-      </c>
-      <c r="Q176" s="12" t="n">
-        <v>-1055</v>
-      </c>
-      <c r="R176" s="12" t="n">
-        <v>-6297</v>
-      </c>
-      <c r="S176" s="12" t="n">
-        <v>11296</v>
-      </c>
-      <c r="T176" s="12" t="n">
-        <v>-7597</v>
-      </c>
-      <c r="U176" s="12" t="n">
-        <v>8584</v>
-      </c>
-      <c r="V176" s="12" t="n">
-        <v>2904</v>
-      </c>
-      <c r="W176" s="12" t="n">
-        <v>-16853</v>
-      </c>
-      <c r="X176" s="12" t="n">
-        <v>95965</v>
+      <c r="E176" s="20" t="n">
+        <v>-587</v>
+      </c>
+      <c r="I176" s="20" t="n">
+        <v>-183</v>
+      </c>
+      <c r="M176" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="O176" s="20" t="n">
+        <v>961</v>
+      </c>
+      <c r="P176" s="20" t="n">
+        <v>-488</v>
+      </c>
+      <c r="Q176" s="20" t="n">
+        <v>549</v>
+      </c>
+      <c r="R176" s="20" t="n">
+        <v>-322</v>
+      </c>
+      <c r="S176" s="20" t="n">
+        <v>-1106</v>
+      </c>
+      <c r="T176" s="20" t="n">
+        <v>2552</v>
+      </c>
+      <c r="U176" s="20" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="V176" s="20" t="n">
+        <v>-587</v>
+      </c>
+      <c r="W176" s="20" t="n">
+        <v>-183</v>
+      </c>
+      <c r="X176" s="20" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="E177" s="20" t="n">
-        <v>903</v>
+        <v>7216</v>
       </c>
       <c r="I177" s="20" t="n">
-        <v>-28</v>
+        <v>11042</v>
       </c>
       <c r="M177" s="20" t="n">
-        <v>413</v>
+        <v>-93480</v>
       </c>
       <c r="O177" s="20" t="n">
-        <v>6</v>
+        <v>10407</v>
       </c>
       <c r="P177" s="20" t="n">
-        <v>-176</v>
+        <v>-1740</v>
       </c>
       <c r="Q177" s="20" t="n">
-        <v>170</v>
+        <v>561</v>
       </c>
       <c r="R177" s="20" t="n">
-        <v>-77</v>
+        <v>10158</v>
       </c>
       <c r="S177" s="20" t="n">
-        <v>-35</v>
+        <v>-10422</v>
       </c>
       <c r="T177" s="20" t="n">
-        <v>551</v>
+        <v>7167</v>
       </c>
       <c r="U177" s="20" t="n">
-        <v>560</v>
+        <v>-1311</v>
       </c>
       <c r="V177" s="20" t="n">
-        <v>903</v>
+        <v>7216</v>
       </c>
       <c r="W177" s="20" t="n">
-        <v>-28</v>
+        <v>11042</v>
       </c>
       <c r="X177" s="20" t="n">
-        <v>413</v>
+        <v>-93480</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="E178" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="I178" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="M178" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="O178" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P178" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q178" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="R178" s="20" t="n">
+        <v>209</v>
+      </c>
+      <c r="S178" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="T178" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="U178" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="V178" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="W178" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="X178" s="20" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="E179" s="20" t="n">
+        <v>-1539</v>
+      </c>
+      <c r="I179" s="20" t="n">
+        <v>-1798</v>
+      </c>
+      <c r="M179" s="20" t="n">
+        <v>-2066</v>
+      </c>
+      <c r="O179" s="20" t="n">
+        <v>-132</v>
+      </c>
+      <c r="P179" s="20" t="n">
+        <v>-214</v>
+      </c>
+      <c r="Q179" s="20" t="n">
+        <v>-391</v>
+      </c>
+      <c r="R179" s="20" t="n">
+        <v>-55</v>
+      </c>
+      <c r="S179" s="20" t="n">
+        <v>-17</v>
+      </c>
+      <c r="T179" s="20" t="n">
+        <v>-108</v>
+      </c>
+      <c r="U179" s="20" t="n">
+        <v>-1199</v>
+      </c>
+      <c r="V179" s="20" t="n">
+        <v>-1539</v>
+      </c>
+      <c r="W179" s="20" t="n">
+        <v>-1798</v>
+      </c>
+      <c r="X179" s="20" t="n">
+        <v>-2066</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="E180" s="20" t="n">
+        <v>-1270</v>
+      </c>
+      <c r="I180" s="20" t="n">
+        <v>-604</v>
+      </c>
+      <c r="M180" s="20" t="n">
+        <v>-1962</v>
+      </c>
+      <c r="O180" s="20" t="n">
+        <v>-709</v>
+      </c>
+      <c r="P180" s="20" t="n">
+        <v>-295</v>
+      </c>
+      <c r="Q180" s="20" t="n">
+        <v>-769</v>
+      </c>
+      <c r="R180" s="20" t="n">
+        <v>-758</v>
+      </c>
+      <c r="S180" s="20" t="n">
+        <v>-1177</v>
+      </c>
+      <c r="T180" s="20" t="n">
+        <v>-1192</v>
+      </c>
+      <c r="U180" s="20" t="n">
+        <v>-2479</v>
+      </c>
+      <c r="V180" s="20" t="n">
+        <v>-1270</v>
+      </c>
+      <c r="W180" s="20" t="n">
+        <v>-604</v>
+      </c>
+      <c r="X180" s="20" t="n">
+        <v>-1962</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="inlineStr">
+        <is>
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="E181" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="20" t="n">
+        <v>525</v>
+      </c>
+      <c r="M181" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" s="20" t="n">
+        <v>525</v>
+      </c>
+      <c r="X181" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>4425</v>
+      </c>
+      <c r="I182" s="12" t="n">
+        <v>9210</v>
+      </c>
+      <c r="M182" s="12" t="n">
+        <v>-97467</v>
+      </c>
+      <c r="O182" s="12" t="n">
+        <v>9586</v>
+      </c>
+      <c r="P182" s="12" t="n">
+        <v>-2229</v>
+      </c>
+      <c r="Q182" s="12" t="n">
+        <v>-570</v>
+      </c>
+      <c r="R182" s="12" t="n">
+        <v>9554</v>
+      </c>
+      <c r="S182" s="12" t="n">
+        <v>-11583</v>
+      </c>
+      <c r="T182" s="12" t="n">
+        <v>5896</v>
+      </c>
+      <c r="U182" s="12" t="n">
+        <v>-4961</v>
+      </c>
+      <c r="V182" s="12" t="n">
+        <v>4425</v>
+      </c>
+      <c r="W182" s="12" t="n">
+        <v>9210</v>
+      </c>
+      <c r="X182" s="12" t="n">
+        <v>-97467</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E183" s="20" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I183" s="20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M183" s="20" t="n">
+        <v>-88</v>
+      </c>
+      <c r="O183" s="20" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P183" s="20" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Q183" s="20" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R183" s="20" t="n">
+        <v>-8</v>
+      </c>
+      <c r="S183" s="20" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T183" s="20" t="n">
+        <v>-149</v>
+      </c>
+      <c r="U183" s="20" t="n">
+        <v>-206</v>
+      </c>
+      <c r="V183" s="20" t="n">
+        <v>-17</v>
+      </c>
+      <c r="W183" s="20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X183" s="20" t="n">
+        <v>-88</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="E184" s="20" t="n">
+        <v>-258</v>
+      </c>
+      <c r="I184" s="20" t="n">
+        <v>-23</v>
+      </c>
+      <c r="M184" s="20" t="n">
+        <v>-26</v>
+      </c>
+      <c r="O184" s="20" t="n">
+        <v>-29</v>
+      </c>
+      <c r="P184" s="20" t="n">
+        <v>-47</v>
+      </c>
+      <c r="Q184" s="20" t="n">
+        <v>-234</v>
+      </c>
+      <c r="R184" s="20" t="n">
+        <v>-8</v>
+      </c>
+      <c r="S184" s="20" t="n">
+        <v>-19</v>
+      </c>
+      <c r="T184" s="20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="U184" s="20" t="n">
+        <v>-82</v>
+      </c>
+      <c r="V184" s="20" t="n">
+        <v>-258</v>
+      </c>
+      <c r="W184" s="20" t="n">
+        <v>-23</v>
+      </c>
+      <c r="X184" s="20" t="n">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
+        <is>
+          <t>투자유가증권 매각</t>
+        </is>
+      </c>
+      <c r="E185" s="20" t="n">
+        <v>741</v>
+      </c>
+      <c r="I185" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" s="20" t="n">
+        <v>741</v>
+      </c>
+      <c r="W185" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E186" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="I186" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M186" s="20" t="n">
+        <v>-248</v>
+      </c>
+      <c r="O186" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P186" s="20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q186" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="R186" s="20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S186" s="20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T186" s="20" t="n">
+        <v>-27</v>
+      </c>
+      <c r="U186" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="V186" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="W186" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X186" s="20" t="n">
+        <v>-248</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E187" s="12" t="n">
+        <v>494</v>
+      </c>
+      <c r="I187" s="12" t="n">
+        <v>-21</v>
+      </c>
+      <c r="M187" s="12" t="n">
+        <v>-362</v>
+      </c>
+      <c r="O187" s="12" t="n">
+        <v>-37</v>
+      </c>
+      <c r="P187" s="12" t="n">
+        <v>-62</v>
+      </c>
+      <c r="Q187" s="12" t="n">
+        <v>-229</v>
+      </c>
+      <c r="R187" s="12" t="n">
+        <v>-17</v>
+      </c>
+      <c r="S187" s="12" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T187" s="12" t="n">
+        <v>-183</v>
+      </c>
+      <c r="U187" s="12" t="n">
+        <v>-263</v>
+      </c>
+      <c r="V187" s="12" t="n">
+        <v>494</v>
+      </c>
+      <c r="W187" s="12" t="n">
+        <v>-21</v>
+      </c>
+      <c r="X187" s="12" t="n">
+        <v>-362</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr">
+        <is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="E188" s="20" t="n">
+        <v>6059</v>
+      </c>
+      <c r="I188" s="20" t="n">
+        <v>-15547</v>
+      </c>
+      <c r="M188" s="20" t="n">
+        <v>98097</v>
+      </c>
+      <c r="O188" s="20" t="n">
+        <v>3364</v>
+      </c>
+      <c r="P188" s="20" t="n">
+        <v>-6554</v>
+      </c>
+      <c r="Q188" s="20" t="n">
+        <v>-511</v>
+      </c>
+      <c r="R188" s="20" t="n">
+        <v>-5648</v>
+      </c>
+      <c r="S188" s="20" t="n">
+        <v>13889</v>
+      </c>
+      <c r="T188" s="20" t="n">
+        <v>-5941</v>
+      </c>
+      <c r="U188" s="20" t="n">
+        <v>10669</v>
+      </c>
+      <c r="V188" s="20" t="n">
+        <v>6059</v>
+      </c>
+      <c r="W188" s="20" t="n">
+        <v>-15547</v>
+      </c>
+      <c r="X188" s="20" t="n">
+        <v>98097</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="18" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="E189" s="20" t="n">
+        <v>-91</v>
+      </c>
+      <c r="I189" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q189" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" s="20" t="n">
+        <v>-36</v>
+      </c>
+      <c r="S189" s="20" t="n">
+        <v>-37</v>
+      </c>
+      <c r="T189" s="20" t="n">
+        <v>-24</v>
+      </c>
+      <c r="U189" s="20" t="n">
+        <v>-43</v>
+      </c>
+      <c r="V189" s="20" t="n">
+        <v>-91</v>
+      </c>
+      <c r="W189" s="20" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q190" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V190" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W190" s="20" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E191" s="20" t="n">
+        <v>-2041</v>
+      </c>
+      <c r="I191" s="20" t="n">
+        <v>-1360</v>
+      </c>
+      <c r="M191" s="20" t="n">
+        <v>-2040</v>
+      </c>
+      <c r="O191" s="20" t="n">
+        <v>-339</v>
+      </c>
+      <c r="P191" s="20" t="n">
+        <v>-408</v>
+      </c>
+      <c r="Q191" s="20" t="n">
+        <v>-544</v>
+      </c>
+      <c r="R191" s="20" t="n">
+        <v>-612</v>
+      </c>
+      <c r="S191" s="20" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="T191" s="20" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="U191" s="20" t="n">
+        <v>-2040</v>
+      </c>
+      <c r="V191" s="20" t="n">
+        <v>-2041</v>
+      </c>
+      <c r="W191" s="20" t="n">
+        <v>-1360</v>
+      </c>
+      <c r="X191" s="20" t="n">
+        <v>-2040</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
+        <is>
+          <t>연결범위 변경 없는 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="E192" s="20" t="n">
+        <v>-1021</v>
+      </c>
+      <c r="I192" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" s="20" t="n">
+        <v>-1965</v>
+      </c>
+      <c r="T192" s="20" t="n">
+        <v>-472</v>
+      </c>
+      <c r="U192" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="20" t="n">
+        <v>-1021</v>
+      </c>
+      <c r="W192" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
+        <is>
+          <t>비지배주주 납입</t>
+        </is>
+      </c>
+      <c r="R193" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" s="20" t="n">
+        <v>431</v>
+      </c>
+      <c r="T193" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="I194" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="M194" s="20" t="n">
+        <v>-90</v>
+      </c>
+      <c r="W194" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="X194" s="20" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="n">
+        <v>2904</v>
+      </c>
+      <c r="I195" s="12" t="n">
+        <v>-16853</v>
+      </c>
+      <c r="M195" s="12" t="n">
+        <v>95965</v>
+      </c>
+      <c r="O195" s="12" t="n">
+        <v>3024</v>
+      </c>
+      <c r="P195" s="12" t="n">
+        <v>-6963</v>
+      </c>
+      <c r="Q195" s="12" t="n">
+        <v>-1055</v>
+      </c>
+      <c r="R195" s="12" t="n">
+        <v>-6297</v>
+      </c>
+      <c r="S195" s="12" t="n">
+        <v>11296</v>
+      </c>
+      <c r="T195" s="12" t="n">
+        <v>-7597</v>
+      </c>
+      <c r="U195" s="12" t="n">
+        <v>8584</v>
+      </c>
+      <c r="V195" s="12" t="n">
+        <v>2904</v>
+      </c>
+      <c r="W195" s="12" t="n">
+        <v>-16853</v>
+      </c>
+      <c r="X195" s="12" t="n">
+        <v>95965</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E196" s="20" t="n">
+        <v>903</v>
+      </c>
+      <c r="I196" s="20" t="n">
+        <v>-28</v>
+      </c>
+      <c r="M196" s="20" t="n">
+        <v>413</v>
+      </c>
+      <c r="O196" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="P196" s="20" t="n">
+        <v>-176</v>
+      </c>
+      <c r="Q196" s="20" t="n">
+        <v>170</v>
+      </c>
+      <c r="R196" s="20" t="n">
+        <v>-77</v>
+      </c>
+      <c r="S196" s="20" t="n">
+        <v>-35</v>
+      </c>
+      <c r="T196" s="20" t="n">
+        <v>551</v>
+      </c>
+      <c r="U196" s="20" t="n">
+        <v>560</v>
+      </c>
+      <c r="V196" s="20" t="n">
+        <v>903</v>
+      </c>
+      <c r="W196" s="20" t="n">
+        <v>-28</v>
+      </c>
+      <c r="X196" s="20" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E178" s="20" t="n">
+      <c r="E197" s="20" t="n">
         <v>8727</v>
       </c>
-      <c r="I178" s="20" t="n">
+      <c r="I197" s="20" t="n">
         <v>-7692</v>
       </c>
-      <c r="M178" s="20" t="n">
+      <c r="M197" s="20" t="n">
         <v>-1451</v>
       </c>
-      <c r="O178" s="20" t="n">
+      <c r="O197" s="20" t="n">
         <v>12579</v>
       </c>
-      <c r="P178" s="20" t="n">
+      <c r="P197" s="20" t="n">
         <v>-9431</v>
       </c>
-      <c r="Q178" s="20" t="n">
+      <c r="Q197" s="20" t="n">
         <v>-1685</v>
       </c>
-      <c r="R178" s="20" t="n">
+      <c r="R197" s="20" t="n">
         <v>3160</v>
       </c>
-      <c r="S178" s="20" t="n">
+      <c r="S197" s="20" t="n">
         <v>-353</v>
       </c>
-      <c r="T178" s="20" t="n">
+      <c r="T197" s="20" t="n">
         <v>-1333</v>
       </c>
-      <c r="U178" s="20" t="n">
+      <c r="U197" s="20" t="n">
         <v>3920</v>
       </c>
-      <c r="V178" s="20" t="n">
+      <c r="V197" s="20" t="n">
         <v>8727</v>
       </c>
-      <c r="W178" s="20" t="n">
+      <c r="W197" s="20" t="n">
         <v>-7692</v>
       </c>
-      <c r="X178" s="20" t="n">
+      <c r="X197" s="20" t="n">
         <v>-1451</v>
       </c>
     </row>
@@ -10667,7 +11558,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -12075,7 +12966,7 @@
       <c r="L42" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="44" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -12127,7 +13018,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -12179,7 +13070,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -12231,7 +13122,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="inlineStr">
+      <c r="A46" s="45" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -12283,7 +13174,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12335,7 +13226,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12387,7 +13278,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12397,43 +13288,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="45">
+      <c r="C49" s="46">
         <f>IFERROR(IF((IF(COUNT('연간'!G50:J50)&lt;4,"",SUM('연간'!G50:J50)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G50:J50)&lt;4,"",SUM('연간'!G50:J50)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="46">
+      <c r="D49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!H50:K50)&lt;4,"",SUM('연간'!H50:K50)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H50:K50)&lt;4,"",SUM('연간'!H50:K50)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="46">
+      <c r="E49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!I50:L50)&lt;4,"",SUM('연간'!I50:L50)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I50:L50)&lt;4,"",SUM('연간'!I50:L50)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="46">
+      <c r="F49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!J50:M50)&lt;4,"",SUM('연간'!J50:M50)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J50:M50)&lt;4,"",SUM('연간'!J50:M50)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="46">
+      <c r="G49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!K50:N50)&lt;4,"",SUM('연간'!K50:N50)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K50:N50)&lt;4,"",SUM('연간'!K50:N50)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="46">
         <f>IFERROR(IF(('연간'!T50)&lt;=0,"적자",H28/('연간'!T50)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="47">
         <f>IFERROR(IF(('연간'!U50)&lt;=0,"적자",I28/('연간'!U50)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="47">
         <f>IFERROR(IF(('연간'!V50)&lt;=0,"적자",J28/('연간'!V50)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="47">
         <f>IFERROR(IF(('연간'!W50)&lt;=0,"적자",K28/('연간'!W50)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="47">
         <f>IFERROR(IF(('연간'!X50)&lt;=0,"적자",L28/('연간'!X50)),"")</f>
         <v/>
       </c>
@@ -12457,7 +13348,7 @@
       <c r="L50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12509,7 +13400,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12561,7 +13452,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12613,7 +13504,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="44" t="inlineStr">
+      <c r="A54" s="45" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12665,7 +13556,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="45" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12717,7 +13608,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12787,7 +13678,7 @@
       <c r="L57" s="23" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12839,7 +13730,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="44" t="inlineStr">
+      <c r="A59" s="45" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12849,49 +13740,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="48">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="48">
+      <c r="D59" s="49">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="49">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="48">
+      <c r="F59" s="49">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="48">
+      <c r="G59" s="49">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="48">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="48">
+      <c r="I59" s="49">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="48">
+      <c r="J59" s="49">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="48">
+      <c r="K59" s="49">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="48">
+      <c r="L59" s="49">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="inlineStr">
+      <c r="A60" s="45" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12901,49 +13792,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <f>IFERROR(C9/(IF(COUNT('연간'!G17:J17)&lt;4,"",SUM('연간'!G17:J17)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="48">
+      <c r="D60" s="49">
         <f>IFERROR(D9/(IF(COUNT('연간'!H17:K17)&lt;4,"",SUM('연간'!H17:K17)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="49">
         <f>IFERROR(E9/(IF(COUNT('연간'!I17:L17)&lt;4,"",SUM('연간'!I17:L17)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="48">
+      <c r="F60" s="49">
         <f>IFERROR(F9/(IF(COUNT('연간'!J17:M17)&lt;4,"",SUM('연간'!J17:M17)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="48">
+      <c r="G60" s="49">
         <f>IFERROR(G9/(IF(COUNT('연간'!K17:N17)&lt;4,"",SUM('연간'!K17:N17)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="47">
+      <c r="H60" s="48">
         <f>IFERROR(H9/('연간'!T17)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="48">
+      <c r="I60" s="49">
         <f>IFERROR(I9/('연간'!U17)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="48">
+      <c r="J60" s="49">
         <f>IFERROR(J9/('연간'!V17)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="48">
+      <c r="K60" s="49">
         <f>IFERROR(K9/('연간'!W17)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="48">
+      <c r="L60" s="49">
         <f>IFERROR(L9/('연간'!X17)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="A61" s="45" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12953,49 +13844,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="48">
         <f>IFERROR(C19/(IF(COUNT('연간'!G17:J17)&lt;4,"",SUM('연간'!G17:J17)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="48">
+      <c r="D61" s="49">
         <f>IFERROR(D19/(IF(COUNT('연간'!H17:K17)&lt;4,"",SUM('연간'!H17:K17)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="49">
         <f>IFERROR(E19/(IF(COUNT('연간'!I17:L17)&lt;4,"",SUM('연간'!I17:L17)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="48">
+      <c r="F61" s="49">
         <f>IFERROR(F19/(IF(COUNT('연간'!J17:M17)&lt;4,"",SUM('연간'!J17:M17)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="48">
+      <c r="G61" s="49">
         <f>IFERROR(G19/(IF(COUNT('연간'!K17:N17)&lt;4,"",SUM('연간'!K17:N17)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="47">
+      <c r="H61" s="48">
         <f>IFERROR(H19/('연간'!T17)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="48">
+      <c r="I61" s="49">
         <f>IFERROR(I19/('연간'!U17)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="48">
+      <c r="J61" s="49">
         <f>IFERROR(J19/('연간'!V17)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="48">
+      <c r="K61" s="49">
         <f>IFERROR(K19/('연간'!W17)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="48">
+      <c r="L61" s="49">
         <f>IFERROR(L19/('연간'!X17)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="44" t="inlineStr">
+      <c r="A62" s="45" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -13005,43 +13896,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="48">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="48">
+      <c r="D62" s="49">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="49">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="49">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="48">
+      <c r="G62" s="49">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="47">
+      <c r="H62" s="48">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="48">
+      <c r="I62" s="49">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="48">
+      <c r="J62" s="49">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="48">
+      <c r="K62" s="49">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="49">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -13065,7 +13956,7 @@
       <c r="L63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="A64" s="45" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -13117,7 +14008,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="A65" s="45" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -13169,7 +14060,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="A66" s="45" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -13221,7 +14112,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="A67" s="45" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15048,24 +15939,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
